--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -841,7 +841,7 @@
         <v>42</v>
       </c>
       <c r="F25" t="n">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -3987,7 +3987,7 @@
         <v>40</v>
       </c>
       <c r="F146" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -4013,7 +4013,7 @@
         <v>41</v>
       </c>
       <c r="F147" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -243,7 +243,7 @@
         <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G2" t="n">
         <v>5.0</v>
@@ -1439,7 +1439,7 @@
         <v>42</v>
       </c>
       <c r="F48" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G48" t="n">
         <v>1.0</v>
@@ -1783,7 +1783,7 @@
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>36.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="62">
@@ -2609,7 +2609,7 @@
         <v>39</v>
       </c>
       <c r="F93" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -3259,7 +3259,7 @@
         <v>41</v>
       </c>
       <c r="F118" t="n">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="G118" t="n">
         <v>14.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1231,7 +1231,7 @@
         <v>42</v>
       </c>
       <c r="F40" t="n">
-        <v>133.0</v>
+        <v>132.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -3285,10 +3285,10 @@
         <v>42</v>
       </c>
       <c r="F119" t="n">
-        <v>532.0</v>
+        <v>533.0</v>
       </c>
       <c r="G119" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="H119" t="n">
         <v>1.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3285,7 +3285,7 @@
         <v>42</v>
       </c>
       <c r="F119" t="n">
-        <v>533.0</v>
+        <v>532.0</v>
       </c>
       <c r="G119" t="n">
         <v>8.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -633,7 +633,7 @@
         <v>41</v>
       </c>
       <c r="F17" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G17" t="n">
         <v>1.0</v>
@@ -711,7 +711,7 @@
         <v>42</v>
       </c>
       <c r="F20" t="n">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -1205,7 +1205,7 @@
         <v>41</v>
       </c>
       <c r="F39" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G39" t="n">
         <v>1.0</v>
@@ -1231,7 +1231,7 @@
         <v>42</v>
       </c>
       <c r="F40" t="n">
-        <v>132.0</v>
+        <v>131.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1595,7 +1595,7 @@
         <v>41</v>
       </c>
       <c r="F54" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -3698,10 +3698,10 @@
         <v>35</v>
       </c>
       <c r="E135" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G135" t="n">
         <v>1.0</v>
@@ -3724,13 +3724,13 @@
         <v>35</v>
       </c>
       <c r="E136" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F136" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3750,10 +3750,10 @@
         <v>35</v>
       </c>
       <c r="E137" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F137" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G137" t="n">
         <v>0.0</v>
@@ -3767,7 +3767,7 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C138" t="s">
         <v>16</v>
@@ -3776,13 +3776,13 @@
         <v>35</v>
       </c>
       <c r="E138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F138" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3802,13 +3802,13 @@
         <v>35</v>
       </c>
       <c r="E139" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G139" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3828,13 +3828,13 @@
         <v>35</v>
       </c>
       <c r="E140" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G140" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3854,7 +3854,7 @@
         <v>35</v>
       </c>
       <c r="E141" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F141" t="n">
         <v>2.0</v>
@@ -3871,7 +3871,7 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C142" t="s">
         <v>16</v>
@@ -3880,10 +3880,10 @@
         <v>35</v>
       </c>
       <c r="E142" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F142" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G142" t="n">
         <v>0.0</v>
@@ -3897,7 +3897,7 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C143" t="s">
         <v>16</v>
@@ -3906,10 +3906,10 @@
         <v>35</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F143" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G143" t="n">
         <v>0.0</v>
@@ -3932,10 +3932,10 @@
         <v>35</v>
       </c>
       <c r="E144" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F144" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>
@@ -3958,10 +3958,10 @@
         <v>35</v>
       </c>
       <c r="E145" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F145" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3984,10 +3984,10 @@
         <v>35</v>
       </c>
       <c r="E146" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F146" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -4001,22 +4001,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C147" t="s">
         <v>16</v>
       </c>
       <c r="D147" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E147" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F147" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4027,22 +4027,22 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C148" t="s">
         <v>16</v>
       </c>
       <c r="D148" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E148" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F148" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4062,13 +4062,13 @@
         <v>36</v>
       </c>
       <c r="E149" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F149" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4088,13 +4088,13 @@
         <v>36</v>
       </c>
       <c r="E150" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F150" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G150" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4114,13 +4114,13 @@
         <v>36</v>
       </c>
       <c r="E151" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G151" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4140,10 +4140,10 @@
         <v>36</v>
       </c>
       <c r="E152" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F152" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G152" t="n">
         <v>0.0</v>
@@ -4157,19 +4157,19 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C153" t="s">
         <v>16</v>
       </c>
       <c r="D153" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E153" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F153" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="n">
         <v>0.0</v>
@@ -4183,22 +4183,22 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C154" t="s">
         <v>16</v>
       </c>
       <c r="D154" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F154" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4209,19 +4209,19 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C155" t="s">
         <v>16</v>
       </c>
       <c r="D155" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F155" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G155" t="n">
         <v>0.0</v>
@@ -4235,7 +4235,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C156" t="s">
         <v>16</v>
@@ -4244,13 +4244,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4261,7 +4261,7 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C157" t="s">
         <v>16</v>
@@ -4270,13 +4270,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F157" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4287,7 +4287,7 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C158" t="s">
         <v>16</v>
@@ -4296,13 +4296,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F158" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G158" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G158" t="n">
-        <v>0.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4322,13 +4322,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F159" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G159" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4348,13 +4348,13 @@
         <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F160" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G160" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H160" t="n">
         <v>0.0</v>
@@ -4374,10 +4374,10 @@
         <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F161" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G161" t="n">
         <v>1.0</v>
@@ -4400,67 +4400,15 @@
         <v>38</v>
       </c>
       <c r="E162" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F162" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G162" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>8</v>
-      </c>
-      <c r="B163" t="s">
-        <v>9</v>
-      </c>
-      <c r="C163" t="s">
-        <v>16</v>
-      </c>
-      <c r="D163" t="s">
-        <v>38</v>
-      </c>
-      <c r="E163" t="s">
-        <v>42</v>
-      </c>
-      <c r="F163" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G163" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>8</v>
-      </c>
-      <c r="B164" t="s">
-        <v>9</v>
-      </c>
-      <c r="C164" t="s">
-        <v>16</v>
-      </c>
-      <c r="D164" t="s">
-        <v>38</v>
-      </c>
-      <c r="E164" t="s">
-        <v>43</v>
-      </c>
-      <c r="F164" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G164" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H164" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1777,13 +1777,13 @@
         <v>42</v>
       </c>
       <c r="F61" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="62">

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -3906,10 +3906,10 @@
         <v>35</v>
       </c>
       <c r="E143" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F143" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G143" t="n">
         <v>0.0</v>
@@ -3932,7 +3932,7 @@
         <v>35</v>
       </c>
       <c r="E144" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F144" t="n">
         <v>10.0</v>
@@ -3958,10 +3958,10 @@
         <v>35</v>
       </c>
       <c r="E145" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F145" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3975,22 +3975,22 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C146" t="s">
         <v>16</v>
       </c>
       <c r="D146" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E146" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F146" t="n">
         <v>4.0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4010,13 +4010,13 @@
         <v>36</v>
       </c>
       <c r="E147" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F147" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G147" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4036,13 +4036,13 @@
         <v>36</v>
       </c>
       <c r="E148" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F148" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G148" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4062,13 +4062,13 @@
         <v>36</v>
       </c>
       <c r="E149" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4088,10 +4088,10 @@
         <v>36</v>
       </c>
       <c r="E150" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F150" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G150" t="n">
         <v>0.0</v>
@@ -4114,10 +4114,10 @@
         <v>36</v>
       </c>
       <c r="E151" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F151" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G151" t="n">
         <v>0.0</v>
@@ -4131,19 +4131,19 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C152" t="s">
         <v>16</v>
       </c>
       <c r="D152" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E152" t="s">
         <v>42</v>
       </c>
       <c r="F152" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="n">
         <v>0.0</v>
@@ -4157,22 +4157,22 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C153" t="s">
         <v>16</v>
       </c>
       <c r="D153" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F153" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4192,13 +4192,13 @@
         <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G154" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4209,7 +4209,7 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C155" t="s">
         <v>16</v>
@@ -4235,7 +4235,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C156" t="s">
         <v>16</v>
@@ -4244,13 +4244,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F156" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4270,13 +4270,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F157" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G157" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4296,13 +4296,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F158" t="n">
         <v>1.0</v>
       </c>
       <c r="G158" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4322,13 +4322,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F159" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G159" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4348,13 +4348,13 @@
         <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F160" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G160" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H160" t="n">
         <v>0.0</v>
@@ -4374,41 +4374,15 @@
         <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F161" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G161" t="n">
         <v>1.0</v>
       </c>
       <c r="H161" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>8</v>
-      </c>
-      <c r="B162" t="s">
-        <v>9</v>
-      </c>
-      <c r="C162" t="s">
-        <v>16</v>
-      </c>
-      <c r="D162" t="s">
-        <v>38</v>
-      </c>
-      <c r="E162" t="s">
-        <v>43</v>
-      </c>
-      <c r="F162" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G162" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H162" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -243,7 +243,7 @@
         <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="G2" t="n">
         <v>5.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -1595,7 +1595,7 @@
         <v>41</v>
       </c>
       <c r="F54" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1777,13 +1777,13 @@
         <v>42</v>
       </c>
       <c r="F61" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="62">
@@ -2086,10 +2086,10 @@
         <v>27</v>
       </c>
       <c r="E73" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G73" t="n">
         <v>1.0</v>
@@ -2112,10 +2112,10 @@
         <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F74" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2138,10 +2138,10 @@
         <v>27</v>
       </c>
       <c r="E75" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F75" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -2155,7 +2155,7 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -2164,10 +2164,10 @@
         <v>27</v>
       </c>
       <c r="E76" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F76" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2190,10 +2190,10 @@
         <v>27</v>
       </c>
       <c r="E77" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F77" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2216,10 +2216,10 @@
         <v>27</v>
       </c>
       <c r="E78" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F78" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -2242,10 +2242,10 @@
         <v>27</v>
       </c>
       <c r="E79" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F79" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2259,19 +2259,19 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E80" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F80" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2294,10 +2294,10 @@
         <v>28</v>
       </c>
       <c r="E81" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F81" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2320,10 +2320,10 @@
         <v>28</v>
       </c>
       <c r="E82" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F82" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2337,7 +2337,7 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -2346,13 +2346,13 @@
         <v>28</v>
       </c>
       <c r="E83" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F83" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2372,10 +2372,10 @@
         <v>28</v>
       </c>
       <c r="E84" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G84" t="n">
         <v>1.0</v>
@@ -2398,13 +2398,13 @@
         <v>28</v>
       </c>
       <c r="E85" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F85" t="n">
-        <v>8.0</v>
+        <v>28.0</v>
       </c>
       <c r="G85" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2424,13 +2424,13 @@
         <v>28</v>
       </c>
       <c r="E86" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F86" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="G86" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2450,13 +2450,13 @@
         <v>28</v>
       </c>
       <c r="E87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="G87" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H87" t="n">
         <v>0.0</v>
@@ -2467,19 +2467,19 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F88" t="n">
-        <v>33.0</v>
+        <v>1.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2502,7 +2502,7 @@
         <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F89" t="n">
         <v>1.0</v>
@@ -2519,7 +2519,7 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -2528,13 +2528,13 @@
         <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F90" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H90" t="n">
         <v>0.0</v>
@@ -2554,16 +2554,16 @@
         <v>29</v>
       </c>
       <c r="E91" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="G91" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="92">
@@ -2580,16 +2580,16 @@
         <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F92" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="G92" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H92" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="93">
@@ -2606,16 +2606,16 @@
         <v>29</v>
       </c>
       <c r="E93" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>5.0</v>
+        <v>43.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
       </c>
       <c r="H93" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="94">
@@ -2632,16 +2632,16 @@
         <v>29</v>
       </c>
       <c r="E94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F94" t="n">
-        <v>43.0</v>
+        <v>12.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
       </c>
       <c r="H94" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="95">
@@ -2649,25 +2649,25 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C95" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E95" t="s">
         <v>41</v>
       </c>
       <c r="F95" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
       </c>
       <c r="H95" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="96">
@@ -2684,7 +2684,7 @@
         <v>30</v>
       </c>
       <c r="E96" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F96" t="n">
         <v>1.0</v>
@@ -2701,7 +2701,7 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C97" t="s">
         <v>15</v>
@@ -2710,13 +2710,13 @@
         <v>30</v>
       </c>
       <c r="E97" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F97" t="n">
-        <v>1.0</v>
+        <v>34.0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2736,13 +2736,13 @@
         <v>30</v>
       </c>
       <c r="E98" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F98" t="n">
-        <v>34.0</v>
+        <v>8.0</v>
       </c>
       <c r="G98" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>
@@ -2762,13 +2762,13 @@
         <v>30</v>
       </c>
       <c r="E99" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F99" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2779,7 +2779,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C100" t="s">
         <v>15</v>
@@ -2788,10 +2788,10 @@
         <v>30</v>
       </c>
       <c r="E100" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F100" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -2805,22 +2805,22 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C101" t="s">
         <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F101" t="n">
         <v>1.0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2840,13 +2840,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F102" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G102" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2866,13 +2866,13 @@
         <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F103" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G103" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H103" t="n">
         <v>0.0</v>
@@ -2883,7 +2883,7 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C104" t="s">
         <v>15</v>
@@ -2892,10 +2892,10 @@
         <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F104" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2918,16 +2918,16 @@
         <v>31</v>
       </c>
       <c r="E105" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="106">
@@ -2944,16 +2944,16 @@
         <v>31</v>
       </c>
       <c r="E106" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F106" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
       </c>
       <c r="H106" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -2961,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C107" t="s">
         <v>15</v>
@@ -2970,13 +2970,13 @@
         <v>31</v>
       </c>
       <c r="E107" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F107" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2996,13 +2996,13 @@
         <v>31</v>
       </c>
       <c r="E108" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G108" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3022,13 +3022,13 @@
         <v>31</v>
       </c>
       <c r="E109" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F109" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G109" t="n">
         <v>4.0</v>
-      </c>
-      <c r="G109" t="n">
-        <v>2.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3048,13 +3048,13 @@
         <v>31</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>6.0</v>
+        <v>17.0</v>
       </c>
       <c r="G110" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3065,22 +3065,22 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C111" t="s">
         <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F111" t="n">
-        <v>17.0</v>
+        <v>2.0</v>
       </c>
       <c r="G111" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3100,13 +3100,13 @@
         <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F112" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G112" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G112" t="n">
-        <v>1.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3126,13 +3126,13 @@
         <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F113" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G113" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3143,7 +3143,7 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C114" t="s">
         <v>15</v>
@@ -3152,13 +3152,13 @@
         <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F114" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3178,7 +3178,7 @@
         <v>32</v>
       </c>
       <c r="E115" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F115" t="n">
         <v>0.0</v>
@@ -3187,7 +3187,7 @@
         <v>1.0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="116">
@@ -3204,16 +3204,16 @@
         <v>32</v>
       </c>
       <c r="E116" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0</v>
+        <v>90.0</v>
       </c>
       <c r="G116" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="H116" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="117">
@@ -3230,13 +3230,13 @@
         <v>32</v>
       </c>
       <c r="E117" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F117" t="n">
-        <v>90.0</v>
+        <v>28.0</v>
       </c>
       <c r="G117" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3256,16 +3256,16 @@
         <v>32</v>
       </c>
       <c r="E118" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>28.0</v>
+        <v>532.0</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="119">
@@ -3282,16 +3282,16 @@
         <v>32</v>
       </c>
       <c r="E119" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>532.0</v>
+        <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H119" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="120">
@@ -3299,22 +3299,22 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C120" t="s">
         <v>15</v>
       </c>
       <c r="D120" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F120" t="n">
         <v>0.0</v>
       </c>
       <c r="G120" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3334,13 +3334,13 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G121" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3351,7 +3351,7 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C122" t="s">
         <v>15</v>
@@ -3360,13 +3360,13 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F122" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3386,13 +3386,13 @@
         <v>33</v>
       </c>
       <c r="E123" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G123" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3403,7 +3403,7 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C124" t="s">
         <v>15</v>
@@ -3412,13 +3412,13 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F124" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3438,13 +3438,13 @@
         <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G125" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3464,10 +3464,10 @@
         <v>33</v>
       </c>
       <c r="E126" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F126" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="G126" t="n">
         <v>2.0</v>
@@ -3490,13 +3490,13 @@
         <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F127" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="G127" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3507,19 +3507,19 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C128" t="s">
         <v>15</v>
       </c>
       <c r="D128" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F128" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -3533,7 +3533,7 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C129" t="s">
         <v>15</v>
@@ -3545,7 +3545,7 @@
         <v>41</v>
       </c>
       <c r="F129" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G129" t="n">
         <v>0.0</v>
@@ -3559,7 +3559,7 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C130" t="s">
         <v>15</v>
@@ -3568,10 +3568,10 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F130" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -3594,16 +3594,16 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F131" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="132">
@@ -3620,16 +3620,16 @@
         <v>34</v>
       </c>
       <c r="E132" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F132" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G132" t="n">
         <v>0.0</v>
       </c>
       <c r="H132" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="133">
@@ -3637,22 +3637,22 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C133" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D133" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E133" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F133" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3672,10 +3672,10 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G134" t="n">
         <v>1.0</v>
@@ -3698,10 +3698,10 @@
         <v>35</v>
       </c>
       <c r="E135" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F135" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G135" t="n">
         <v>1.0</v>
@@ -3724,13 +3724,13 @@
         <v>35</v>
       </c>
       <c r="E136" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G136" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3741,7 +3741,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C137" t="s">
         <v>16</v>
@@ -3750,13 +3750,13 @@
         <v>35</v>
       </c>
       <c r="E137" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F137" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3776,13 +3776,13 @@
         <v>35</v>
       </c>
       <c r="E138" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F138" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3802,13 +3802,13 @@
         <v>35</v>
       </c>
       <c r="E139" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G139" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3828,7 +3828,7 @@
         <v>35</v>
       </c>
       <c r="E140" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F140" t="n">
         <v>2.0</v>
@@ -3845,7 +3845,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C141" t="s">
         <v>16</v>
@@ -3854,10 +3854,10 @@
         <v>35</v>
       </c>
       <c r="E141" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F141" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G141" t="n">
         <v>0.0</v>
@@ -3880,10 +3880,10 @@
         <v>35</v>
       </c>
       <c r="E142" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F142" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G142" t="n">
         <v>0.0</v>
@@ -3906,7 +3906,7 @@
         <v>35</v>
       </c>
       <c r="E143" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F143" t="n">
         <v>10.0</v>
@@ -3932,10 +3932,10 @@
         <v>35</v>
       </c>
       <c r="E144" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F144" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>
@@ -3949,22 +3949,22 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
       </c>
       <c r="D145" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E145" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F145" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3984,13 +3984,13 @@
         <v>36</v>
       </c>
       <c r="E146" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F146" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G146" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4010,13 +4010,13 @@
         <v>36</v>
       </c>
       <c r="E147" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F147" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4036,13 +4036,13 @@
         <v>36</v>
       </c>
       <c r="E148" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G148" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4062,10 +4062,10 @@
         <v>36</v>
       </c>
       <c r="E149" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F149" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G149" t="n">
         <v>0.0</v>
@@ -4088,10 +4088,10 @@
         <v>36</v>
       </c>
       <c r="E150" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F150" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G150" t="n">
         <v>0.0</v>
@@ -4105,19 +4105,19 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C151" t="s">
         <v>16</v>
       </c>
       <c r="D151" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E151" t="s">
         <v>42</v>
       </c>
       <c r="F151" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G151" t="n">
         <v>0.0</v>
@@ -4131,22 +4131,22 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C152" t="s">
         <v>16</v>
       </c>
       <c r="D152" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E152" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F152" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4166,13 +4166,13 @@
         <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G153" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4183,7 +4183,7 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C154" t="s">
         <v>16</v>
@@ -4209,7 +4209,7 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C155" t="s">
         <v>16</v>
@@ -4218,13 +4218,13 @@
         <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F155" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4244,13 +4244,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F156" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G156" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4270,13 +4270,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F157" t="n">
         <v>1.0</v>
       </c>
       <c r="G157" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4296,13 +4296,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F158" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G158" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4322,13 +4322,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F159" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G159" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4348,41 +4348,15 @@
         <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F160" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G160" t="n">
         <v>1.0</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>8</v>
-      </c>
-      <c r="B161" t="s">
-        <v>9</v>
-      </c>
-      <c r="C161" t="s">
-        <v>16</v>
-      </c>
-      <c r="D161" t="s">
-        <v>38</v>
-      </c>
-      <c r="E161" t="s">
-        <v>43</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G161" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H161" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -607,7 +607,7 @@
         <v>39</v>
       </c>
       <c r="F16" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -3259,7 +3259,7 @@
         <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>532.0</v>
+        <v>531.0</v>
       </c>
       <c r="G118" t="n">
         <v>8.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1179,7 +1179,7 @@
         <v>39</v>
       </c>
       <c r="F38" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G38" t="n">
         <v>4.0</v>
@@ -1231,7 +1231,7 @@
         <v>42</v>
       </c>
       <c r="F40" t="n">
-        <v>131.0</v>
+        <v>130.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -2843,7 +2843,7 @@
         <v>41</v>
       </c>
       <c r="F102" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G102" t="n">
         <v>2.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="47">
   <si>
     <t>Area</t>
   </si>
@@ -370,10 +370,10 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -396,10 +396,10 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G8" t="n">
         <v>0.0</v>
@@ -413,7 +413,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -422,13 +422,13 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H9" t="n">
         <v>0.0</v>
@@ -439,7 +439,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -451,10 +451,10 @@
         <v>39</v>
       </c>
       <c r="F10" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="G10" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
@@ -465,7 +465,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -474,13 +474,13 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H11" t="n">
         <v>0.0</v>
@@ -491,7 +491,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -500,10 +500,10 @@
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n">
-        <v>35.0</v>
+        <v>2.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -526,13 +526,13 @@
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>79.0</v>
+        <v>26.0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H13" t="n">
         <v>0.0</v>
@@ -543,22 +543,22 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F14" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H14" t="n">
         <v>0.0</v>
@@ -569,19 +569,19 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
-        <v>13.0</v>
+        <v>32.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -595,22 +595,22 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F16" t="n">
-        <v>7.0</v>
+        <v>68.0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H16" t="n">
         <v>0.0</v>
@@ -621,7 +621,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -630,13 +630,13 @@
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F17" t="n">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H17" t="n">
         <v>0.0</v>
@@ -647,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
@@ -656,10 +656,10 @@
         <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -682,13 +682,13 @@
         <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H19" t="n">
         <v>0.0</v>
@@ -708,13 +708,13 @@
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" t="n">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H20" t="n">
         <v>0.0</v>
@@ -725,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -734,7 +734,7 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F21" t="n">
         <v>1.0</v>
@@ -751,7 +751,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -760,10 +760,10 @@
         <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -777,22 +777,22 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0</v>
+        <v>23.0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H23" t="n">
         <v>0.0</v>
@@ -812,13 +812,13 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H24" t="n">
         <v>0.0</v>
@@ -838,10 +838,10 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F25" t="n">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -855,7 +855,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -864,13 +864,13 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0</v>
+        <v>20.0</v>
       </c>
       <c r="G26" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -890,13 +890,13 @@
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F27" t="n">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -916,13 +916,13 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="G28" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -942,13 +942,13 @@
         <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F29" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H29" t="n">
         <v>0.0</v>
@@ -959,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -968,10 +968,10 @@
         <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F30" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -994,7 +994,7 @@
         <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F31" t="n">
         <v>3.0</v>
@@ -1020,10 +1020,10 @@
         <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F32" t="n">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1037,22 +1037,22 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="G33" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H33" t="n">
         <v>0.0</v>
@@ -1072,13 +1072,13 @@
         <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>
@@ -1101,10 +1101,10 @@
         <v>42</v>
       </c>
       <c r="F35" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H35" t="n">
         <v>0.0</v>
@@ -1115,7 +1115,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
@@ -1124,10 +1124,10 @@
         <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F36" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G36" t="n">
         <v>1.0</v>
@@ -1141,7 +1141,7 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -1150,13 +1150,13 @@
         <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G37" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1167,7 +1167,7 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -1179,10 +1179,10 @@
         <v>39</v>
       </c>
       <c r="F38" t="n">
-        <v>15.0</v>
+        <v>2.0</v>
       </c>
       <c r="G38" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1193,7 +1193,7 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -1202,10 +1202,10 @@
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F39" t="n">
-        <v>23.0</v>
+        <v>2.0</v>
       </c>
       <c r="G39" t="n">
         <v>1.0</v>
@@ -1219,7 +1219,7 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F40" t="n">
-        <v>130.0</v>
+        <v>1.0</v>
       </c>
       <c r="G40" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>
@@ -1254,10 +1254,10 @@
         <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="G41" t="n">
         <v>1.0</v>
@@ -1271,22 +1271,22 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E42" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F42" t="n">
-        <v>4.0</v>
+        <v>18.0</v>
       </c>
       <c r="G42" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1297,22 +1297,22 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F43" t="n">
-        <v>23.0</v>
+        <v>119.0</v>
       </c>
       <c r="G43" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1332,13 +1332,13 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1358,13 +1358,13 @@
         <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F45" t="n">
-        <v>1.0</v>
+        <v>23.0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1381,10 +1381,10 @@
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F46" t="n">
         <v>0.0</v>
@@ -1407,19 +1407,19 @@
         <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F47" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G47" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="48">
@@ -1436,7 +1436,7 @@
         <v>23</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
@@ -1462,16 +1462,16 @@
         <v>23</v>
       </c>
       <c r="E49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G49" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="50">
@@ -1488,13 +1488,13 @@
         <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F50" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1505,22 +1505,22 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
         <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F51" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G51" t="n">
         <v>3.0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1537,16 +1537,16 @@
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G52" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1557,7 +1557,7 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
@@ -1566,7 +1566,7 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F53" t="n">
         <v>3.0</v>
@@ -1592,13 +1592,13 @@
         <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F54" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1609,7 +1609,7 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C55" t="s">
         <v>13</v>
@@ -1618,13 +1618,13 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G55" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1635,7 +1635,7 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -1644,10 +1644,10 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F56" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1670,13 +1670,13 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F57" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1696,10 +1696,10 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F58" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -1716,22 +1716,22 @@
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F59" t="n">
-        <v>39.0</v>
+        <v>9.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
       </c>
       <c r="H59" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
@@ -1742,22 +1742,22 @@
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F60" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
       </c>
       <c r="H60" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -1774,16 +1774,16 @@
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F61" t="n">
-        <v>173.0</v>
+        <v>39.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>33.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="62">
@@ -1791,25 +1791,25 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F62" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="63">
@@ -1817,25 +1817,25 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F63" t="n">
-        <v>2.0</v>
+        <v>173.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="64">
@@ -1852,10 +1852,10 @@
         <v>26</v>
       </c>
       <c r="E64" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>38.0</v>
+        <v>1.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1869,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -1878,10 +1878,10 @@
         <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F65" t="n">
-        <v>19.0</v>
+        <v>2.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1904,10 +1904,10 @@
         <v>26</v>
       </c>
       <c r="E66" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F66" t="n">
-        <v>1.0</v>
+        <v>35.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1930,10 +1930,10 @@
         <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F67" t="n">
-        <v>30.0</v>
+        <v>3.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1947,22 +1947,22 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0</v>
+        <v>66.0</v>
       </c>
       <c r="G68" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1973,7 +1973,7 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -1982,10 +1982,10 @@
         <v>27</v>
       </c>
       <c r="E69" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F69" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G69" t="n">
         <v>1.0</v>
@@ -1999,7 +1999,7 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -2011,10 +2011,10 @@
         <v>39</v>
       </c>
       <c r="F70" t="n">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H70" t="n">
         <v>0.0</v>
@@ -2025,7 +2025,7 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -2034,16 +2034,16 @@
         <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F71" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H71" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -2051,7 +2051,7 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
@@ -2060,13 +2060,13 @@
         <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F72" t="n">
-        <v>4.0</v>
+        <v>17.0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2077,7 +2077,7 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -2086,16 +2086,16 @@
         <v>27</v>
       </c>
       <c r="E73" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F73" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="G73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="74">
@@ -2103,19 +2103,19 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E74" t="s">
         <v>41</v>
       </c>
       <c r="F74" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2129,16 +2129,16 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F75" t="n">
         <v>1.0</v>
@@ -2155,19 +2155,19 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E76" t="s">
         <v>39</v>
       </c>
       <c r="F76" t="n">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2181,19 +2181,19 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F77" t="n">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2207,22 +2207,22 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F78" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2233,22 +2233,22 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E79" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F79" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2259,7 +2259,7 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
@@ -2268,13 +2268,13 @@
         <v>28</v>
       </c>
       <c r="E80" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F80" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2285,7 +2285,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
@@ -2294,10 +2294,10 @@
         <v>28</v>
       </c>
       <c r="E81" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F81" t="n">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2311,7 +2311,7 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -2323,7 +2323,7 @@
         <v>42</v>
       </c>
       <c r="F82" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2337,7 +2337,7 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -2346,10 +2346,10 @@
         <v>28</v>
       </c>
       <c r="E83" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G83" t="n">
         <v>1.0</v>
@@ -2363,7 +2363,7 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
@@ -2378,7 +2378,7 @@
         <v>8.0</v>
       </c>
       <c r="G84" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2389,7 +2389,7 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -2398,13 +2398,13 @@
         <v>28</v>
       </c>
       <c r="E85" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F85" t="n">
-        <v>28.0</v>
+        <v>16.0</v>
       </c>
       <c r="G85" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2415,16 +2415,16 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F86" t="n">
         <v>0.0</v>
@@ -2441,25 +2441,25 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E87" t="s">
         <v>42</v>
       </c>
       <c r="F87" t="n">
-        <v>33.0</v>
+        <v>9.0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="88">
@@ -2467,7 +2467,7 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -2476,16 +2476,16 @@
         <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F88" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="89">
@@ -2493,7 +2493,7 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -2502,16 +2502,16 @@
         <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F89" t="n">
-        <v>1.0</v>
+        <v>44.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="90">
@@ -2528,16 +2528,16 @@
         <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="G90" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="91">
@@ -2545,25 +2545,25 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F91" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="G91" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H91" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="92">
@@ -2571,16 +2571,16 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F92" t="n">
         <v>5.0</v>
@@ -2589,7 +2589,7 @@
         <v>0.0</v>
       </c>
       <c r="H92" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="93">
@@ -2597,25 +2597,25 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F93" t="n">
-        <v>43.0</v>
+        <v>2.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
       </c>
       <c r="H93" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="94">
@@ -2623,25 +2623,25 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E94" t="s">
         <v>41</v>
       </c>
       <c r="F94" t="n">
-        <v>12.0</v>
+        <v>28.0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H94" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="95">
@@ -2649,7 +2649,7 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C95" t="s">
         <v>15</v>
@@ -2658,13 +2658,13 @@
         <v>30</v>
       </c>
       <c r="E95" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F95" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2675,7 +2675,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C96" t="s">
         <v>15</v>
@@ -2684,7 +2684,7 @@
         <v>30</v>
       </c>
       <c r="E96" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F96" t="n">
         <v>1.0</v>
@@ -2701,7 +2701,7 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C97" t="s">
         <v>15</v>
@@ -2713,10 +2713,10 @@
         <v>41</v>
       </c>
       <c r="F97" t="n">
-        <v>34.0</v>
+        <v>3.0</v>
       </c>
       <c r="G97" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2727,7 +2727,7 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C98" t="s">
         <v>15</v>
@@ -2739,10 +2739,10 @@
         <v>42</v>
       </c>
       <c r="F98" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G98" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>
@@ -2753,22 +2753,22 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C99" t="s">
         <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E99" t="s">
         <v>39</v>
       </c>
       <c r="F99" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2779,22 +2779,22 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C100" t="s">
         <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E100" t="s">
         <v>41</v>
       </c>
       <c r="F100" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2814,13 +2814,13 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F101" t="n">
         <v>1.0</v>
       </c>
       <c r="G101" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2831,7 +2831,7 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
         <v>15</v>
@@ -2840,13 +2840,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F102" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G102" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2857,7 +2857,7 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
         <v>15</v>
@@ -2866,16 +2866,16 @@
         <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F103" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="104">
@@ -2892,7 +2892,7 @@
         <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F104" t="n">
         <v>1.0</v>
@@ -2909,7 +2909,7 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C105" t="s">
         <v>15</v>
@@ -2918,16 +2918,16 @@
         <v>31</v>
       </c>
       <c r="E105" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F105" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="106">
@@ -2935,7 +2935,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C106" t="s">
         <v>15</v>
@@ -2944,13 +2944,13 @@
         <v>31</v>
       </c>
       <c r="E106" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F106" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -2970,13 +2970,13 @@
         <v>31</v>
       </c>
       <c r="E107" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G107" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2996,10 +2996,10 @@
         <v>31</v>
       </c>
       <c r="E108" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F108" t="n">
-        <v>4.0</v>
+        <v>18.0</v>
       </c>
       <c r="G108" t="n">
         <v>2.0</v>
@@ -3013,22 +3013,22 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C109" t="s">
         <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F109" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G109" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3039,19 +3039,19 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C110" t="s">
         <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F110" t="n">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="G110" t="n">
         <v>2.0</v>
@@ -3074,13 +3074,13 @@
         <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F111" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3091,7 +3091,7 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C112" t="s">
         <v>15</v>
@@ -3100,13 +3100,13 @@
         <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F112" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G112" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3117,7 +3117,7 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C113" t="s">
         <v>15</v>
@@ -3126,16 +3126,16 @@
         <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F113" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="114">
@@ -3152,13 +3152,13 @@
         <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0</v>
+        <v>90.0</v>
       </c>
       <c r="G114" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3178,16 +3178,16 @@
         <v>32</v>
       </c>
       <c r="E115" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="G115" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="H115" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="116">
@@ -3204,16 +3204,16 @@
         <v>32</v>
       </c>
       <c r="E116" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>90.0</v>
+        <v>531.0</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="117">
@@ -3230,13 +3230,13 @@
         <v>32</v>
       </c>
       <c r="E117" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F117" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="G117" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3253,19 +3253,19 @@
         <v>15</v>
       </c>
       <c r="D118" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F118" t="n">
-        <v>531.0</v>
+        <v>1.0</v>
       </c>
       <c r="G118" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="H118" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -3279,16 +3279,16 @@
         <v>15</v>
       </c>
       <c r="D119" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F119" t="n">
         <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3299,7 +3299,7 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C120" t="s">
         <v>15</v>
@@ -3311,10 +3311,10 @@
         <v>41</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G120" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3325,7 +3325,7 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C121" t="s">
         <v>15</v>
@@ -3337,10 +3337,10 @@
         <v>42</v>
       </c>
       <c r="F121" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="G121" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3351,22 +3351,22 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C122" t="s">
         <v>15</v>
       </c>
       <c r="D122" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E122" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G122" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3377,25 +3377,25 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C123" t="s">
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E123" t="s">
         <v>41</v>
       </c>
       <c r="F123" t="n">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="G123" t="n">
         <v>0.0</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="124">
@@ -3409,16 +3409,16 @@
         <v>15</v>
       </c>
       <c r="D124" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E124" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="G124" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3429,22 +3429,22 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C125" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E125" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F125" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G125" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3455,22 +3455,22 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C126" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E126" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F126" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="G126" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3481,22 +3481,22 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C127" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D127" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E127" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F127" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3510,16 +3510,16 @@
         <v>10</v>
       </c>
       <c r="C128" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E128" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F128" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
@@ -3536,19 +3536,19 @@
         <v>11</v>
       </c>
       <c r="C129" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D129" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E129" t="s">
         <v>41</v>
       </c>
       <c r="F129" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3559,22 +3559,22 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C130" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D130" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E130" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F130" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3585,25 +3585,25 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C131" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D131" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E131" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F131" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
       </c>
       <c r="H131" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="132">
@@ -3611,19 +3611,19 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E132" t="s">
         <v>42</v>
       </c>
       <c r="F132" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G132" t="n">
         <v>0.0</v>
@@ -3637,7 +3637,7 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C133" t="s">
         <v>16</v>
@@ -3646,13 +3646,13 @@
         <v>35</v>
       </c>
       <c r="E133" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G133" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3663,7 +3663,7 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C134" t="s">
         <v>16</v>
@@ -3672,13 +3672,13 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F134" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G134" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3689,7 +3689,7 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C135" t="s">
         <v>16</v>
@@ -3698,13 +3698,13 @@
         <v>35</v>
       </c>
       <c r="E135" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="G135" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3715,7 +3715,7 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C136" t="s">
         <v>16</v>
@@ -3727,7 +3727,7 @@
         <v>42</v>
       </c>
       <c r="F136" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G136" t="n">
         <v>0.0</v>
@@ -3747,16 +3747,16 @@
         <v>16</v>
       </c>
       <c r="D137" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F137" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G137" t="n">
         <v>3.0</v>
-      </c>
-      <c r="G137" t="n">
-        <v>4.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3773,16 +3773,16 @@
         <v>16</v>
       </c>
       <c r="D138" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G138" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3799,16 +3799,16 @@
         <v>16</v>
       </c>
       <c r="D139" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3825,13 +3825,13 @@
         <v>16</v>
       </c>
       <c r="D140" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F140" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G140" t="n">
         <v>0.0</v>
@@ -3845,19 +3845,19 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
         <v>16</v>
       </c>
       <c r="D141" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F141" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G141" t="n">
         <v>0.0</v>
@@ -3871,19 +3871,19 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C142" t="s">
         <v>16</v>
       </c>
       <c r="D142" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F142" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="G142" t="n">
         <v>0.0</v>
@@ -3903,13 +3903,13 @@
         <v>16</v>
       </c>
       <c r="D143" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F143" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G143" t="n">
         <v>0.0</v>
@@ -3923,22 +3923,22 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C144" t="s">
         <v>16</v>
       </c>
       <c r="D144" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E144" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F144" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3949,22 +3949,22 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
       </c>
       <c r="D145" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E145" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F145" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G145" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3981,16 +3981,16 @@
         <v>16</v>
       </c>
       <c r="D146" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E146" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F146" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G146" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4001,22 +4001,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C147" t="s">
         <v>16</v>
       </c>
       <c r="D147" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E147" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G147" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4027,13 +4027,13 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C148" t="s">
         <v>16</v>
       </c>
       <c r="D148" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E148" t="s">
         <v>44</v>
@@ -4042,7 +4042,7 @@
         <v>1.0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4053,22 +4053,22 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C149" t="s">
         <v>16</v>
       </c>
       <c r="D149" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E149" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F149" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4079,22 +4079,22 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C150" t="s">
         <v>16</v>
       </c>
       <c r="D150" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E150" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F150" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4111,16 +4111,16 @@
         <v>16</v>
       </c>
       <c r="D151" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E151" t="s">
         <v>42</v>
       </c>
       <c r="F151" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4131,7 +4131,7 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C152" t="s">
         <v>16</v>
@@ -4140,7 +4140,7 @@
         <v>38</v>
       </c>
       <c r="E152" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F152" t="n">
         <v>0.0</v>
@@ -4149,214 +4149,6 @@
         <v>1.0</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>8</v>
-      </c>
-      <c r="B153" t="s">
-        <v>10</v>
-      </c>
-      <c r="C153" t="s">
-        <v>16</v>
-      </c>
-      <c r="D153" t="s">
-        <v>38</v>
-      </c>
-      <c r="E153" t="s">
-        <v>40</v>
-      </c>
-      <c r="F153" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>8</v>
-      </c>
-      <c r="B154" t="s">
-        <v>11</v>
-      </c>
-      <c r="C154" t="s">
-        <v>16</v>
-      </c>
-      <c r="D154" t="s">
-        <v>38</v>
-      </c>
-      <c r="E154" t="s">
-        <v>40</v>
-      </c>
-      <c r="F154" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G154" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H154" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>8</v>
-      </c>
-      <c r="B155" t="s">
-        <v>9</v>
-      </c>
-      <c r="C155" t="s">
-        <v>16</v>
-      </c>
-      <c r="D155" t="s">
-        <v>38</v>
-      </c>
-      <c r="E155" t="s">
-        <v>46</v>
-      </c>
-      <c r="F155" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>8</v>
-      </c>
-      <c r="B156" t="s">
-        <v>9</v>
-      </c>
-      <c r="C156" t="s">
-        <v>16</v>
-      </c>
-      <c r="D156" t="s">
-        <v>38</v>
-      </c>
-      <c r="E156" t="s">
-        <v>44</v>
-      </c>
-      <c r="F156" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G156" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>8</v>
-      </c>
-      <c r="B157" t="s">
-        <v>9</v>
-      </c>
-      <c r="C157" t="s">
-        <v>16</v>
-      </c>
-      <c r="D157" t="s">
-        <v>38</v>
-      </c>
-      <c r="E157" t="s">
-        <v>39</v>
-      </c>
-      <c r="F157" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H157" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>8</v>
-      </c>
-      <c r="B158" t="s">
-        <v>9</v>
-      </c>
-      <c r="C158" t="s">
-        <v>16</v>
-      </c>
-      <c r="D158" t="s">
-        <v>38</v>
-      </c>
-      <c r="E158" t="s">
-        <v>40</v>
-      </c>
-      <c r="F158" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="G158" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H158" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>8</v>
-      </c>
-      <c r="B159" t="s">
-        <v>9</v>
-      </c>
-      <c r="C159" t="s">
-        <v>16</v>
-      </c>
-      <c r="D159" t="s">
-        <v>38</v>
-      </c>
-      <c r="E159" t="s">
-        <v>42</v>
-      </c>
-      <c r="F159" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G159" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H159" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>8</v>
-      </c>
-      <c r="B160" t="s">
-        <v>9</v>
-      </c>
-      <c r="C160" t="s">
-        <v>16</v>
-      </c>
-      <c r="D160" t="s">
-        <v>38</v>
-      </c>
-      <c r="E160" t="s">
-        <v>43</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G160" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H160" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -607,7 +607,7 @@
         <v>42</v>
       </c>
       <c r="F16" t="n">
-        <v>68.0</v>
+        <v>67.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -1361,7 +1361,7 @@
         <v>41</v>
       </c>
       <c r="F45" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="G45" t="n">
         <v>3.0</v>
@@ -1829,13 +1829,13 @@
         <v>42</v>
       </c>
       <c r="F63" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
       </c>
       <c r="H63" t="n">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="64">
@@ -3207,7 +3207,7 @@
         <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>531.0</v>
+        <v>530.0</v>
       </c>
       <c r="G116" t="n">
         <v>8.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -867,7 +867,7 @@
         <v>42</v>
       </c>
       <c r="F26" t="n">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -1335,10 +1335,10 @@
         <v>46</v>
       </c>
       <c r="F44" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G44" t="n">
         <v>4.0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -867,7 +867,7 @@
         <v>42</v>
       </c>
       <c r="F26" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -3181,7 +3181,7 @@
         <v>41</v>
       </c>
       <c r="F115" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="G115" t="n">
         <v>14.0</v>
@@ -3207,7 +3207,7 @@
         <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>530.0</v>
+        <v>529.0</v>
       </c>
       <c r="G116" t="n">
         <v>8.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -971,7 +971,7 @@
         <v>42</v>
       </c>
       <c r="F30" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -1777,7 +1777,7 @@
         <v>39</v>
       </c>
       <c r="F61" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1829,7 +1829,7 @@
         <v>42</v>
       </c>
       <c r="F63" t="n">
-        <v>172.0</v>
+        <v>171.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1959,7 +1959,7 @@
         <v>42</v>
       </c>
       <c r="F68" t="n">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2037,7 +2037,7 @@
         <v>41</v>
       </c>
       <c r="F71" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G71" t="n">
         <v>1.0</v>
@@ -2089,7 +2089,7 @@
         <v>40</v>
       </c>
       <c r="F73" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -2401,7 +2401,7 @@
         <v>42</v>
       </c>
       <c r="F85" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -3207,7 +3207,7 @@
         <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>529.0</v>
+        <v>528.0</v>
       </c>
       <c r="G116" t="n">
         <v>8.0</v>
@@ -3389,7 +3389,7 @@
         <v>41</v>
       </c>
       <c r="F123" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G123" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -246,7 +246,7 @@
         <v>10.0</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H2" t="n">
         <v>0.0</v>
@@ -841,7 +841,7 @@
         <v>41</v>
       </c>
       <c r="F25" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -893,10 +893,10 @@
         <v>39</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G27" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -916,13 +916,13 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F28" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -942,13 +942,13 @@
         <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0</v>
+        <v>24.0</v>
       </c>
       <c r="G29" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H29" t="n">
         <v>0.0</v>
@@ -1829,13 +1829,13 @@
         <v>42</v>
       </c>
       <c r="F63" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
       </c>
       <c r="H63" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="64">
@@ -1959,7 +1959,7 @@
         <v>42</v>
       </c>
       <c r="F68" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2193,7 +2193,7 @@
         <v>42</v>
       </c>
       <c r="F77" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2511,7 +2511,7 @@
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="90">
@@ -2999,7 +2999,7 @@
         <v>42</v>
       </c>
       <c r="F108" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G108" t="n">
         <v>2.0</v>
@@ -3207,7 +3207,7 @@
         <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>528.0</v>
+        <v>529.0</v>
       </c>
       <c r="G116" t="n">
         <v>8.0</v>
@@ -3337,7 +3337,7 @@
         <v>42</v>
       </c>
       <c r="F121" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G121" t="n">
         <v>2.0</v>
@@ -3470,7 +3470,7 @@
         <v>6.0</v>
       </c>
       <c r="G126" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3646,13 +3646,13 @@
         <v>35</v>
       </c>
       <c r="E133" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F133" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3672,10 +3672,10 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F134" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G134" t="n">
         <v>0.0</v>
@@ -3698,7 +3698,7 @@
         <v>35</v>
       </c>
       <c r="E135" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F135" t="n">
         <v>10.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1309,7 +1309,7 @@
         <v>42</v>
       </c>
       <c r="F43" t="n">
-        <v>119.0</v>
+        <v>118.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -2505,7 +2505,7 @@
         <v>40</v>
       </c>
       <c r="F89" t="n">
-        <v>44.0</v>
+        <v>43.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -295,7 +295,7 @@
         <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G4" t="n">
         <v>3.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -945,7 +945,7 @@
         <v>41</v>
       </c>
       <c r="F29" t="n">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -1309,7 +1309,7 @@
         <v>42</v>
       </c>
       <c r="F43" t="n">
-        <v>118.0</v>
+        <v>117.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3207,10 +3207,10 @@
         <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>529.0</v>
+        <v>530.0</v>
       </c>
       <c r="G116" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H116" t="n">
         <v>1.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="48">
   <si>
     <t>Area</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>II</t>
+  </si>
+  <si>
+    <t>III</t>
   </si>
   <si>
     <t>Emilia romagna</t>
@@ -234,13 +237,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
         <v>10.0</v>
@@ -260,13 +263,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
         <v>18.0</v>
@@ -286,13 +289,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
         <v>9.0</v>
@@ -312,13 +315,13 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" t="n">
         <v>34.0</v>
@@ -338,13 +341,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
         <v>1.0</v>
@@ -364,13 +367,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
         <v>2.0</v>
@@ -390,13 +393,13 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
         <v>6.0</v>
@@ -416,13 +419,13 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" t="n">
         <v>13.0</v>
@@ -442,13 +445,13 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -468,13 +471,13 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
         <v>1.0</v>
@@ -494,13 +497,13 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
         <v>2.0</v>
@@ -520,13 +523,13 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
         <v>26.0</v>
@@ -546,13 +549,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -572,13 +575,13 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
         <v>32.0</v>
@@ -598,13 +601,13 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="n">
         <v>67.0</v>
@@ -624,13 +627,13 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
         <v>2.0</v>
@@ -650,16 +653,16 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -676,13 +679,13 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
         <v>11.0</v>
@@ -702,13 +705,13 @@
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
         <v>11.0</v>
@@ -728,13 +731,13 @@
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F21" t="n">
         <v>1.0</v>
@@ -754,13 +757,13 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22" t="n">
         <v>1.0</v>
@@ -780,16 +783,16 @@
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" t="n">
-        <v>23.0</v>
+        <v>28.0</v>
       </c>
       <c r="G23" t="n">
         <v>0.0</v>
@@ -806,13 +809,13 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F24" t="n">
         <v>3.0</v>
@@ -832,13 +835,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
         <v>11.0</v>
@@ -858,13 +861,13 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" t="n">
         <v>20.0</v>
@@ -884,13 +887,13 @@
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F27" t="n">
         <v>2.0</v>
@@ -910,13 +913,13 @@
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -936,13 +939,13 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F29" t="n">
         <v>23.0</v>
@@ -962,13 +965,13 @@
         <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F30" t="n">
         <v>14.0</v>
@@ -988,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F31" t="n">
         <v>3.0</v>
@@ -1014,13 +1017,13 @@
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F32" t="n">
         <v>2.0</v>
@@ -1040,13 +1043,13 @@
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F33" t="n">
         <v>11.0</v>
@@ -1066,13 +1069,13 @@
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F34" t="n">
         <v>2.0</v>
@@ -1092,13 +1095,13 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F35" t="n">
         <v>11.0</v>
@@ -1118,13 +1121,13 @@
         <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36" t="n">
         <v>0.0</v>
@@ -1144,13 +1147,13 @@
         <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F37" t="n">
         <v>5.0</v>
@@ -1170,13 +1173,13 @@
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F38" t="n">
         <v>2.0</v>
@@ -1196,13 +1199,13 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F39" t="n">
         <v>2.0</v>
@@ -1222,13 +1225,13 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>
@@ -1248,13 +1251,13 @@
         <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F41" t="n">
         <v>13.0</v>
@@ -1274,13 +1277,13 @@
         <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F42" t="n">
         <v>18.0</v>
@@ -1300,13 +1303,13 @@
         <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F43" t="n">
         <v>117.0</v>
@@ -1326,13 +1329,13 @@
         <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F44" t="n">
         <v>2.0</v>
@@ -1352,13 +1355,13 @@
         <v>11</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F45" t="n">
         <v>22.0</v>
@@ -1378,13 +1381,13 @@
         <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F46" t="n">
         <v>0.0</v>
@@ -1404,13 +1407,13 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F47" t="n">
         <v>1.0</v>
@@ -1430,13 +1433,13 @@
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
@@ -1456,13 +1459,13 @@
         <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F49" t="n">
         <v>2.0</v>
@@ -1482,13 +1485,13 @@
         <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F50" t="n">
         <v>0.0</v>
@@ -1508,13 +1511,13 @@
         <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F51" t="n">
         <v>0.0</v>
@@ -1534,13 +1537,13 @@
         <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F52" t="n">
         <v>2.0</v>
@@ -1560,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E53" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F53" t="n">
         <v>3.0</v>
@@ -1586,13 +1589,13 @@
         <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F54" t="n">
         <v>0.0</v>
@@ -1612,13 +1615,13 @@
         <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F55" t="n">
         <v>3.0</v>
@@ -1638,13 +1641,13 @@
         <v>11</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E56" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F56" t="n">
         <v>10.0</v>
@@ -1664,13 +1667,13 @@
         <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E57" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F57" t="n">
         <v>0.0</v>
@@ -1690,13 +1693,13 @@
         <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F58" t="n">
         <v>2.0</v>
@@ -1716,13 +1719,13 @@
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F59" t="n">
         <v>9.0</v>
@@ -1742,13 +1745,13 @@
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F60" t="n">
         <v>1.0</v>
@@ -1768,13 +1771,13 @@
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E61" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F61" t="n">
         <v>40.0</v>
@@ -1794,13 +1797,13 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F62" t="n">
         <v>16.0</v>
@@ -1820,13 +1823,13 @@
         <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E63" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F63" t="n">
         <v>172.0</v>
@@ -1846,13 +1849,13 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E64" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>1.0</v>
@@ -1872,13 +1875,13 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E65" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F65" t="n">
         <v>2.0</v>
@@ -1898,13 +1901,13 @@
         <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E66" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F66" t="n">
         <v>35.0</v>
@@ -1924,13 +1927,13 @@
         <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E67" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F67" t="n">
         <v>3.0</v>
@@ -1950,13 +1953,13 @@
         <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E68" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F68" t="n">
         <v>66.0</v>
@@ -1976,13 +1979,13 @@
         <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E69" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F69" t="n">
         <v>0.0</v>
@@ -2002,13 +2005,13 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E70" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F70" t="n">
         <v>18.0</v>
@@ -2028,13 +2031,13 @@
         <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F71" t="n">
         <v>10.0</v>
@@ -2054,13 +2057,13 @@
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E72" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F72" t="n">
         <v>17.0</v>
@@ -2080,13 +2083,13 @@
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E73" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F73" t="n">
         <v>8.0</v>
@@ -2106,13 +2109,13 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E74" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F74" t="n">
         <v>9.0</v>
@@ -2132,13 +2135,13 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E75" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F75" t="n">
         <v>1.0</v>
@@ -2158,13 +2161,13 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F76" t="n">
         <v>2.0</v>
@@ -2184,13 +2187,13 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F77" t="n">
         <v>19.0</v>
@@ -2210,13 +2213,13 @@
         <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F78" t="n">
         <v>0.0</v>
@@ -2236,13 +2239,13 @@
         <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F79" t="n">
         <v>1.0</v>
@@ -2262,13 +2265,13 @@
         <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D80" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
@@ -2288,13 +2291,13 @@
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
         <v>11.0</v>
@@ -2314,13 +2317,13 @@
         <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F82" t="n">
         <v>4.0</v>
@@ -2340,13 +2343,13 @@
         <v>9</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F83" t="n">
         <v>8.0</v>
@@ -2366,13 +2369,13 @@
         <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F84" t="n">
         <v>8.0</v>
@@ -2392,13 +2395,13 @@
         <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F85" t="n">
         <v>15.0</v>
@@ -2418,13 +2421,13 @@
         <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E86" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F86" t="n">
         <v>0.0</v>
@@ -2444,13 +2447,13 @@
         <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F87" t="n">
         <v>9.0</v>
@@ -2470,13 +2473,13 @@
         <v>9</v>
       </c>
       <c r="C88" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E88" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F88" t="n">
         <v>5.0</v>
@@ -2496,13 +2499,13 @@
         <v>9</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F89" t="n">
         <v>43.0</v>
@@ -2522,13 +2525,13 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F90" t="n">
         <v>13.0</v>
@@ -2548,13 +2551,13 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E91" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F91" t="n">
         <v>2.0</v>
@@ -2574,13 +2577,13 @@
         <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E92" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F92" t="n">
         <v>5.0</v>
@@ -2600,13 +2603,13 @@
         <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D93" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E93" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F93" t="n">
         <v>2.0</v>
@@ -2626,19 +2629,19 @@
         <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F94" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="G94" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H94" t="n">
         <v>0.0</v>
@@ -2652,19 +2655,19 @@
         <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D95" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F95" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G95" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2678,16 +2681,16 @@
         <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F96" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -2701,22 +2704,22 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F97" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2727,22 +2730,22 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F98" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>
@@ -2753,22 +2756,22 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C99" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D99" t="s">
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F99" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2779,22 +2782,22 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C100" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D100" t="s">
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F100" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G100" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2808,19 +2811,19 @@
         <v>10</v>
       </c>
       <c r="C101" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D101" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F101" t="n">
         <v>1.0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2831,22 +2834,22 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D102" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E102" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F102" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2857,25 +2860,25 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E103" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F103" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
       </c>
       <c r="H103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -2886,16 +2889,16 @@
         <v>11</v>
       </c>
       <c r="C104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D104" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E104" t="s">
         <v>42</v>
       </c>
       <c r="F104" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2909,22 +2912,22 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D105" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H105" t="n">
         <v>0.0</v>
@@ -2935,22 +2938,22 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D106" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F106" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G106" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -2961,25 +2964,25 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D107" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F107" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G107" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="108">
@@ -2990,19 +2993,19 @@
         <v>9</v>
       </c>
       <c r="C108" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F108" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
       <c r="G108" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3013,22 +3016,22 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C109" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D109" t="s">
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F109" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G109" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G109" t="n">
-        <v>1.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3039,22 +3042,22 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C110" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D110" t="s">
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G110" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3065,22 +3068,22 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C111" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D111" t="s">
         <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F111" t="n">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3091,19 +3094,19 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C112" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E112" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G112" t="n">
         <v>1.0</v>
@@ -3117,25 +3120,25 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C113" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D113" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G113" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H113" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="114">
@@ -3143,22 +3146,22 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C114" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D114" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F114" t="n">
-        <v>90.0</v>
+        <v>3.0</v>
       </c>
       <c r="G114" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3172,19 +3175,19 @@
         <v>9</v>
       </c>
       <c r="C115" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F115" t="n">
-        <v>27.0</v>
+        <v>0.0</v>
       </c>
       <c r="G115" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3198,22 +3201,22 @@
         <v>9</v>
       </c>
       <c r="C116" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D116" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F116" t="n">
-        <v>530.0</v>
+        <v>0.0</v>
       </c>
       <c r="G116" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H116" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="117">
@@ -3224,19 +3227,19 @@
         <v>9</v>
       </c>
       <c r="C117" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D117" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0</v>
+        <v>90.0</v>
       </c>
       <c r="G117" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3250,19 +3253,19 @@
         <v>9</v>
       </c>
       <c r="C118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D118" t="s">
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>1.0</v>
+        <v>27.0</v>
       </c>
       <c r="G118" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3276,22 +3279,22 @@
         <v>9</v>
       </c>
       <c r="C119" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D119" t="s">
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0</v>
+        <v>530.0</v>
       </c>
       <c r="G119" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="120">
@@ -3302,19 +3305,19 @@
         <v>9</v>
       </c>
       <c r="C120" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D120" t="s">
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F120" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="G120" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3328,19 +3331,19 @@
         <v>9</v>
       </c>
       <c r="C121" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E121" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F121" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G121" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3354,19 +3357,19 @@
         <v>9</v>
       </c>
       <c r="C122" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D122" t="s">
         <v>34</v>
       </c>
       <c r="E122" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F122" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3380,22 +3383,22 @@
         <v>9</v>
       </c>
       <c r="C123" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D123" t="s">
         <v>34</v>
       </c>
       <c r="E123" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F123" t="n">
-        <v>16.0</v>
+        <v>7.0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H123" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="124">
@@ -3406,19 +3409,19 @@
         <v>9</v>
       </c>
       <c r="C124" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D124" t="s">
         <v>34</v>
       </c>
       <c r="E124" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F124" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3429,7 +3432,7 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C125" t="s">
         <v>16</v>
@@ -3438,13 +3441,13 @@
         <v>35</v>
       </c>
       <c r="E125" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G125" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3455,7 +3458,7 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C126" t="s">
         <v>16</v>
@@ -3464,16 +3467,16 @@
         <v>35</v>
       </c>
       <c r="E126" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F126" t="n">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="G126" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="127">
@@ -3481,7 +3484,7 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C127" t="s">
         <v>16</v>
@@ -3493,10 +3496,10 @@
         <v>43</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="G127" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3510,19 +3513,19 @@
         <v>10</v>
       </c>
       <c r="C128" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D128" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E128" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F128" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3533,22 +3536,22 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C129" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D129" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E129" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F129" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G129" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3559,22 +3562,22 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C130" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D130" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E130" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F130" t="n">
         <v>0.0</v>
       </c>
       <c r="G130" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3585,19 +3588,19 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D131" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E131" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F131" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G131" t="n">
         <v>0.0</v>
@@ -3614,19 +3617,19 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D132" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E132" t="s">
         <v>42</v>
       </c>
       <c r="F132" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3637,22 +3640,22 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C133" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D133" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F133" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3663,19 +3666,19 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D134" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F134" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G134" t="n">
         <v>0.0</v>
@@ -3689,19 +3692,19 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C135" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D135" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F135" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G135" t="n">
         <v>0.0</v>
@@ -3718,19 +3721,19 @@
         <v>9</v>
       </c>
       <c r="C136" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D136" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E136" t="s">
         <v>42</v>
       </c>
       <c r="F136" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3741,22 +3744,22 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C137" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D137" t="s">
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F137" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G137" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3767,10 +3770,10 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C138" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D138" t="s">
         <v>36</v>
@@ -3779,10 +3782,10 @@
         <v>41</v>
       </c>
       <c r="F138" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G138" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3793,10 +3796,10 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C139" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D139" t="s">
         <v>36</v>
@@ -3805,10 +3808,10 @@
         <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G139" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3822,19 +3825,19 @@
         <v>11</v>
       </c>
       <c r="C140" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E140" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F140" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3848,19 +3851,19 @@
         <v>11</v>
       </c>
       <c r="C141" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E141" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F141" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3874,19 +3877,19 @@
         <v>11</v>
       </c>
       <c r="C142" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F142" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3897,16 +3900,16 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C143" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D143" t="s">
         <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F143" t="n">
         <v>1.0</v>
@@ -3923,22 +3926,22 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C144" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G144" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3949,19 +3952,19 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C145" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F145" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3975,19 +3978,19 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C146" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D146" t="s">
         <v>38</v>
       </c>
       <c r="E146" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F146" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -4001,22 +4004,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C147" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E147" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F147" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4027,22 +4030,22 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C148" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E148" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F148" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G148" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4053,22 +4056,22 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C149" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E149" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F149" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4082,16 +4085,16 @@
         <v>9</v>
       </c>
       <c r="C150" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E150" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F150" t="n">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="G150" t="n">
         <v>3.0</v>
@@ -4108,19 +4111,19 @@
         <v>9</v>
       </c>
       <c r="C151" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E151" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F151" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G151" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4134,21 +4137,99 @@
         <v>9</v>
       </c>
       <c r="C152" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E152" t="s">
+        <v>40</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>8</v>
+      </c>
+      <c r="B153" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" t="s">
+        <v>39</v>
+      </c>
+      <c r="E153" t="s">
+        <v>41</v>
+      </c>
+      <c r="F153" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" t="s">
+        <v>39</v>
+      </c>
+      <c r="E154" t="s">
         <v>43</v>
       </c>
-      <c r="F152" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G152" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H152" t="n">
+      <c r="F154" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>39</v>
+      </c>
+      <c r="E155" t="s">
+        <v>44</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H155" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -792,7 +792,7 @@
         <v>43</v>
       </c>
       <c r="F23" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="G23" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3288,7 +3288,7 @@
         <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>530.0</v>
+        <v>529.0</v>
       </c>
       <c r="G119" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1780,7 +1780,7 @@
         <v>40</v>
       </c>
       <c r="F61" t="n">
-        <v>40.0</v>
+        <v>39.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -818,7 +818,7 @@
         <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G24" t="n">
         <v>1.0</v>
@@ -870,7 +870,7 @@
         <v>43</v>
       </c>
       <c r="F26" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1474,7 +1474,7 @@
         <v>2.0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="50">
@@ -1832,7 +1832,7 @@
         <v>43</v>
       </c>
       <c r="F63" t="n">
-        <v>172.0</v>
+        <v>171.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -3782,7 +3782,7 @@
         <v>41</v>
       </c>
       <c r="F138" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -3808,7 +3808,7 @@
         <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G139" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3262,7 +3262,7 @@
         <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="G118" t="n">
         <v>14.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1832,7 +1832,7 @@
         <v>43</v>
       </c>
       <c r="F63" t="n">
-        <v>171.0</v>
+        <v>170.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -3288,7 +3288,7 @@
         <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>529.0</v>
+        <v>528.0</v>
       </c>
       <c r="G119" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -584,7 +584,7 @@
         <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -610,7 +610,7 @@
         <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -324,7 +324,7 @@
         <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -532,7 +532,7 @@
         <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="G13" t="n">
         <v>3.0</v>
@@ -610,7 +610,7 @@
         <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -948,7 +948,7 @@
         <v>42</v>
       </c>
       <c r="F29" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -1104,7 +1104,7 @@
         <v>43</v>
       </c>
       <c r="F35" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G35" t="n">
         <v>1.0</v>
@@ -1312,7 +1312,7 @@
         <v>43</v>
       </c>
       <c r="F43" t="n">
-        <v>117.0</v>
+        <v>116.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1910,7 +1910,7 @@
         <v>40</v>
       </c>
       <c r="F66" t="n">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1962,7 +1962,7 @@
         <v>43</v>
       </c>
       <c r="F68" t="n">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2066,7 +2066,7 @@
         <v>43</v>
       </c>
       <c r="F72" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G72" t="n">
         <v>1.0</v>
@@ -2404,7 +2404,7 @@
         <v>43</v>
       </c>
       <c r="F85" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2846,7 +2846,7 @@
         <v>42</v>
       </c>
       <c r="F102" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G102" t="n">
         <v>2.0</v>
@@ -2898,7 +2898,7 @@
         <v>42</v>
       </c>
       <c r="F104" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2924,7 +2924,7 @@
         <v>43</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -3054,10 +3054,10 @@
         <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G110" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3080,7 +3080,7 @@
         <v>43</v>
       </c>
       <c r="F111" t="n">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="G111" t="n">
         <v>2.0</v>
@@ -3288,7 +3288,7 @@
         <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>528.0</v>
+        <v>531.0</v>
       </c>
       <c r="G119" t="n">
         <v>7.0</v>
@@ -3395,7 +3395,7 @@
         <v>7.0</v>
       </c>
       <c r="G123" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3808,7 +3808,7 @@
         <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G139" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="48">
   <si>
     <t>Area</t>
   </si>
@@ -584,7 +584,7 @@
         <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -818,10 +818,10 @@
         <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H24" t="n">
         <v>0.0</v>
@@ -844,7 +844,7 @@
         <v>42</v>
       </c>
       <c r="F25" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -870,7 +870,7 @@
         <v>43</v>
       </c>
       <c r="F26" t="n">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -896,10 +896,10 @@
         <v>40</v>
       </c>
       <c r="F27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G27" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -948,7 +948,7 @@
         <v>42</v>
       </c>
       <c r="F29" t="n">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -974,7 +974,7 @@
         <v>43</v>
       </c>
       <c r="F30" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -1101,10 +1101,10 @@
         <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F35" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="G35" t="n">
         <v>1.0</v>
@@ -1127,10 +1127,10 @@
         <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="G36" t="n">
         <v>1.0</v>
@@ -1153,13 +1153,13 @@
         <v>22</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F37" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1286,10 +1286,10 @@
         <v>42</v>
       </c>
       <c r="F42" t="n">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="G42" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1312,7 +1312,7 @@
         <v>43</v>
       </c>
       <c r="F43" t="n">
-        <v>116.0</v>
+        <v>115.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1572,7 +1572,7 @@
         <v>42</v>
       </c>
       <c r="F53" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1650,7 +1650,7 @@
         <v>42</v>
       </c>
       <c r="F56" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -3103,10 +3103,10 @@
         <v>33</v>
       </c>
       <c r="E112" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F112" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G112" t="n">
         <v>1.0</v>
@@ -3132,7 +3132,7 @@
         <v>42</v>
       </c>
       <c r="F113" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G113" t="n">
         <v>2.0</v>
@@ -3158,7 +3158,7 @@
         <v>43</v>
       </c>
       <c r="F114" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G114" t="n">
         <v>0.0</v>
@@ -3172,7 +3172,7 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C115" t="s">
         <v>16</v>
@@ -3181,10 +3181,10 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G115" t="n">
         <v>1.0</v>
@@ -3198,7 +3198,7 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C116" t="s">
         <v>16</v>
@@ -3207,16 +3207,16 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G116" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H116" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="117">
@@ -3224,7 +3224,7 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C117" t="s">
         <v>16</v>
@@ -3233,13 +3233,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F117" t="n">
-        <v>90.0</v>
+        <v>2.0</v>
       </c>
       <c r="G117" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3259,16 +3259,16 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F118" t="n">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="119">
@@ -3285,16 +3285,16 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F119" t="n">
-        <v>531.0</v>
+        <v>90.0</v>
       </c>
       <c r="G119" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="H119" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="120">
@@ -3311,13 +3311,13 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
       <c r="G120" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3334,19 +3334,19 @@
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F121" t="n">
-        <v>1.0</v>
+        <v>531.0</v>
       </c>
       <c r="G121" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="122">
@@ -3360,16 +3360,16 @@
         <v>16</v>
       </c>
       <c r="D122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F122" t="n">
         <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3389,13 +3389,13 @@
         <v>34</v>
       </c>
       <c r="E123" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F123" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G123" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3415,13 +3415,13 @@
         <v>34</v>
       </c>
       <c r="E124" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F124" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G124" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3438,16 +3438,16 @@
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E125" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F125" t="n">
         <v>7.0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3464,19 +3464,19 @@
         <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E126" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F126" t="n">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H126" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="127">
@@ -3493,10 +3493,10 @@
         <v>35</v>
       </c>
       <c r="E127" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F127" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="G127" t="n">
         <v>0.0</v>
@@ -3510,25 +3510,25 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C128" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E128" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="G128" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="129">
@@ -3536,22 +3536,22 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C129" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D129" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E129" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F129" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G129" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3571,7 +3571,7 @@
         <v>36</v>
       </c>
       <c r="E130" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F130" t="n">
         <v>0.0</v>
@@ -3597,13 +3597,13 @@
         <v>36</v>
       </c>
       <c r="E131" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>
@@ -3614,7 +3614,7 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C132" t="s">
         <v>17</v>
@@ -3623,13 +3623,13 @@
         <v>36</v>
       </c>
       <c r="E132" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F132" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3640,7 +3640,7 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -3649,13 +3649,13 @@
         <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G133" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3675,13 +3675,13 @@
         <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F134" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3701,13 +3701,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F135" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G135" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3718,7 +3718,7 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C136" t="s">
         <v>17</v>
@@ -3727,13 +3727,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F136" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="G136" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3744,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -3753,10 +3753,10 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F137" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G137" t="n">
         <v>0.0</v>
@@ -3779,13 +3779,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F138" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3805,10 +3805,10 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F139" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G139" t="n">
         <v>0.0</v>
@@ -3822,22 +3822,22 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F140" t="n">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="G140" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3848,22 +3848,22 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F141" t="n">
         <v>5.0</v>
       </c>
       <c r="G141" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3883,13 +3883,13 @@
         <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G142" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3909,13 +3909,13 @@
         <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F143" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3935,13 +3935,13 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F144" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3961,10 +3961,10 @@
         <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F145" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3978,19 +3978,19 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E146" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F146" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -4004,22 +4004,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E147" t="s">
         <v>43</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G147" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4030,19 +4030,19 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E148" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F148" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -4056,7 +4056,7 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
@@ -4065,13 +4065,13 @@
         <v>39</v>
       </c>
       <c r="E149" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F149" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4082,7 +4082,7 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
@@ -4091,13 +4091,13 @@
         <v>39</v>
       </c>
       <c r="E150" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F150" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G150" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4108,7 +4108,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4117,13 +4117,13 @@
         <v>39</v>
       </c>
       <c r="E151" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F151" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G151" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4143,13 +4143,13 @@
         <v>39</v>
       </c>
       <c r="E152" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F152" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G152" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4169,13 +4169,13 @@
         <v>39</v>
       </c>
       <c r="E153" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F153" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4195,10 +4195,10 @@
         <v>39</v>
       </c>
       <c r="E154" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F154" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G154" t="n">
         <v>1.0</v>
@@ -4221,15 +4221,67 @@
         <v>39</v>
       </c>
       <c r="E155" t="s">
+        <v>41</v>
+      </c>
+      <c r="F155" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>8</v>
+      </c>
+      <c r="B156" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" t="s">
+        <v>39</v>
+      </c>
+      <c r="E156" t="s">
+        <v>43</v>
+      </c>
+      <c r="F156" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
+        <v>39</v>
+      </c>
+      <c r="E157" t="s">
         <v>44</v>
       </c>
-      <c r="F155" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H155" t="n">
+      <c r="F157" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H157" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -610,7 +610,7 @@
         <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -3054,7 +3054,7 @@
         <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G110" t="n">
         <v>5.0</v>
@@ -3340,7 +3340,7 @@
         <v>43</v>
       </c>
       <c r="F121" t="n">
-        <v>531.0</v>
+        <v>530.0</v>
       </c>
       <c r="G121" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3080,7 +3080,7 @@
         <v>43</v>
       </c>
       <c r="F111" t="n">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="G111" t="n">
         <v>2.0</v>
@@ -3288,7 +3288,7 @@
         <v>40</v>
       </c>
       <c r="F119" t="n">
-        <v>90.0</v>
+        <v>89.0</v>
       </c>
       <c r="G119" t="n">
         <v>12.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3340,7 +3340,7 @@
         <v>43</v>
       </c>
       <c r="F121" t="n">
-        <v>530.0</v>
+        <v>529.0</v>
       </c>
       <c r="G121" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3340,7 +3340,7 @@
         <v>43</v>
       </c>
       <c r="F121" t="n">
-        <v>529.0</v>
+        <v>528.0</v>
       </c>
       <c r="G121" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3340,7 +3340,7 @@
         <v>43</v>
       </c>
       <c r="F121" t="n">
-        <v>528.0</v>
+        <v>529.0</v>
       </c>
       <c r="G121" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3678,7 +3678,7 @@
         <v>42</v>
       </c>
       <c r="F134" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G134" t="n">
         <v>4.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -2745,7 +2745,7 @@
         <v>1.0</v>
       </c>
       <c r="G98" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -2508,7 +2508,7 @@
         <v>41</v>
       </c>
       <c r="F89" t="n">
-        <v>43.0</v>
+        <v>42.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="48">
   <si>
     <t>Area</t>
   </si>
@@ -662,7 +662,7 @@
         <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -1104,7 +1104,7 @@
         <v>42</v>
       </c>
       <c r="F35" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G35" t="n">
         <v>1.0</v>
@@ -1468,7 +1468,7 @@
         <v>42</v>
       </c>
       <c r="F49" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G49" t="n">
         <v>2.0</v>
@@ -2271,13 +2271,13 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G80" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2297,10 +2297,10 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F81" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2314,7 +2314,7 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C82" t="s">
         <v>15</v>
@@ -2323,13 +2323,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F82" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2349,13 +2349,13 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F83" t="n">
         <v>8.0</v>
       </c>
       <c r="G83" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2375,10 +2375,10 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F84" t="n">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2398,16 +2398,16 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E85" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F85" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2427,16 +2427,16 @@
         <v>30</v>
       </c>
       <c r="E86" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="G86" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="87">
@@ -2453,16 +2453,16 @@
         <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F87" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="G87" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H87" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="88">
@@ -2479,16 +2479,16 @@
         <v>30</v>
       </c>
       <c r="E88" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F88" t="n">
-        <v>5.0</v>
+        <v>42.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
       </c>
       <c r="H88" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="89">
@@ -2505,16 +2505,16 @@
         <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F89" t="n">
-        <v>42.0</v>
+        <v>13.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="90">
@@ -2522,25 +2522,25 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E90" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F90" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
       </c>
       <c r="H90" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="91">
@@ -2557,10 +2557,10 @@
         <v>31</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F91" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2583,10 +2583,10 @@
         <v>31</v>
       </c>
       <c r="E92" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F92" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2600,7 +2600,7 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C93" t="s">
         <v>16</v>
@@ -2609,13 +2609,13 @@
         <v>31</v>
       </c>
       <c r="E93" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F93" t="n">
-        <v>2.0</v>
+        <v>27.0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -2635,13 +2635,13 @@
         <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F94" t="n">
-        <v>27.0</v>
+        <v>1.0</v>
       </c>
       <c r="G94" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H94" t="n">
         <v>0.0</v>
@@ -2661,10 +2661,10 @@
         <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F95" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2678,7 +2678,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2687,13 +2687,13 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F96" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2713,13 +2713,13 @@
         <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F97" t="n">
         <v>1.0</v>
       </c>
       <c r="G97" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2730,7 +2730,7 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C98" t="s">
         <v>16</v>
@@ -2739,10 +2739,10 @@
         <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F98" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
@@ -2765,10 +2765,10 @@
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F99" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2782,22 +2782,22 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
       </c>
       <c r="D100" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E100" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F100" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2817,13 +2817,13 @@
         <v>32</v>
       </c>
       <c r="E101" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F101" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G101" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2843,13 +2843,13 @@
         <v>32</v>
       </c>
       <c r="E102" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F102" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G102" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2860,7 +2860,7 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
@@ -2869,16 +2869,16 @@
         <v>32</v>
       </c>
       <c r="E103" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F103" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="104">
@@ -2895,10 +2895,10 @@
         <v>32</v>
       </c>
       <c r="E104" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F104" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2912,7 +2912,7 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C105" t="s">
         <v>16</v>
@@ -2921,10 +2921,10 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F105" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2947,7 +2947,7 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F106" t="n">
         <v>1.0</v>
@@ -2956,7 +2956,7 @@
         <v>0.0</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="107">
@@ -2964,7 +2964,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C107" t="s">
         <v>16</v>
@@ -2973,16 +2973,16 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F107" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H107" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="108">
@@ -2999,13 +2999,13 @@
         <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G108" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3025,13 +3025,13 @@
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F109" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="G109" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3051,13 +3051,13 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F110" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
       <c r="G110" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3068,22 +3068,22 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C111" t="s">
         <v>16</v>
       </c>
       <c r="D111" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E111" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F111" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="G111" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3103,13 +3103,13 @@
         <v>33</v>
       </c>
       <c r="E112" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F112" t="n">
         <v>0.0</v>
       </c>
       <c r="G112" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3129,13 +3129,13 @@
         <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G113" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3146,7 +3146,7 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C114" t="s">
         <v>16</v>
@@ -3155,13 +3155,13 @@
         <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F114" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3181,13 +3181,13 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F115" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G115" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3207,10 +3207,10 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F116" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G116" t="n">
         <v>0.0</v>
@@ -3224,7 +3224,7 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C117" t="s">
         <v>16</v>
@@ -3233,16 +3233,16 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F117" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H117" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="118">
@@ -3259,16 +3259,16 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0</v>
+        <v>89.0</v>
       </c>
       <c r="G118" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="H118" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -3285,13 +3285,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F119" t="n">
-        <v>89.0</v>
+        <v>26.0</v>
       </c>
       <c r="G119" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3311,16 +3311,16 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F120" t="n">
-        <v>26.0</v>
+        <v>526.0</v>
       </c>
       <c r="G120" t="n">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="121">
@@ -3337,16 +3337,16 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F121" t="n">
-        <v>528.0</v>
+        <v>0.0</v>
       </c>
       <c r="G121" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H121" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="122">
@@ -3360,16 +3360,16 @@
         <v>16</v>
       </c>
       <c r="D122" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E122" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G122" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3389,10 +3389,10 @@
         <v>34</v>
       </c>
       <c r="E123" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F123" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G123" t="n">
         <v>1.0</v>
@@ -3415,13 +3415,13 @@
         <v>34</v>
       </c>
       <c r="E124" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G124" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3441,10 +3441,10 @@
         <v>34</v>
       </c>
       <c r="E125" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F125" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="G125" t="n">
         <v>2.0</v>
@@ -3464,16 +3464,16 @@
         <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E126" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F126" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="G126" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3493,16 +3493,16 @@
         <v>35</v>
       </c>
       <c r="E127" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F127" t="n">
-        <v>7.0</v>
+        <v>16.0</v>
       </c>
       <c r="G127" t="n">
         <v>0.0</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="128">
@@ -3519,16 +3519,16 @@
         <v>35</v>
       </c>
       <c r="E128" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F128" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="G128" t="n">
         <v>0.0</v>
       </c>
       <c r="H128" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="129">
@@ -3536,22 +3536,22 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C129" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D129" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E129" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F129" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3571,13 +3571,13 @@
         <v>36</v>
       </c>
       <c r="E130" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G130" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3597,13 +3597,13 @@
         <v>36</v>
       </c>
       <c r="E131" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F131" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G131" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>
@@ -3623,13 +3623,13 @@
         <v>36</v>
       </c>
       <c r="E132" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G132" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3640,7 +3640,7 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -3649,13 +3649,13 @@
         <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F133" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3675,13 +3675,13 @@
         <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F134" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G134" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G134" t="n">
-        <v>4.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3701,13 +3701,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G135" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3727,7 +3727,7 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F136" t="n">
         <v>2.0</v>
@@ -3744,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -3753,13 +3753,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F137" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3779,13 +3779,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F138" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G138" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3805,10 +3805,10 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F139" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G139" t="n">
         <v>0.0</v>
@@ -3831,10 +3831,10 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F140" t="n">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="G140" t="n">
         <v>0.0</v>
@@ -3848,22 +3848,22 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E141" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F141" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3883,13 +3883,13 @@
         <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F142" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G142" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3909,13 +3909,13 @@
         <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F143" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3935,13 +3935,13 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G144" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3961,10 +3961,10 @@
         <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F145" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3987,10 +3987,10 @@
         <v>37</v>
       </c>
       <c r="E146" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F146" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -4004,19 +4004,19 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E147" t="s">
         <v>43</v>
       </c>
       <c r="F147" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -4030,22 +4030,22 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E148" t="s">
         <v>43</v>
       </c>
       <c r="F148" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4065,13 +4065,13 @@
         <v>39</v>
       </c>
       <c r="E149" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4082,7 +4082,7 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
@@ -4108,7 +4108,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4117,13 +4117,13 @@
         <v>39</v>
       </c>
       <c r="E151" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F151" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4143,13 +4143,13 @@
         <v>39</v>
       </c>
       <c r="E152" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F152" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4169,13 +4169,13 @@
         <v>39</v>
       </c>
       <c r="E153" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F153" t="n">
         <v>1.0</v>
       </c>
       <c r="G153" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4195,13 +4195,13 @@
         <v>39</v>
       </c>
       <c r="E154" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F154" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G154" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4221,13 +4221,13 @@
         <v>39</v>
       </c>
       <c r="E155" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F155" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G155" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4247,41 +4247,15 @@
         <v>39</v>
       </c>
       <c r="E156" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F156" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G156" t="n">
         <v>1.0</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>8</v>
-      </c>
-      <c r="B157" t="s">
-        <v>9</v>
-      </c>
-      <c r="C157" t="s">
-        <v>17</v>
-      </c>
-      <c r="D157" t="s">
-        <v>39</v>
-      </c>
-      <c r="E157" t="s">
-        <v>44</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H157" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3314,7 +3314,7 @@
         <v>43</v>
       </c>
       <c r="F120" t="n">
-        <v>526.0</v>
+        <v>525.0</v>
       </c>
       <c r="G120" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1832,7 +1832,7 @@
         <v>43</v>
       </c>
       <c r="F63" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -3314,7 +3314,7 @@
         <v>43</v>
       </c>
       <c r="F120" t="n">
-        <v>525.0</v>
+        <v>524.0</v>
       </c>
       <c r="G120" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3262,7 +3262,7 @@
         <v>40</v>
       </c>
       <c r="F118" t="n">
-        <v>89.0</v>
+        <v>88.0</v>
       </c>
       <c r="G118" t="n">
         <v>12.0</v>
@@ -3314,7 +3314,7 @@
         <v>43</v>
       </c>
       <c r="F120" t="n">
-        <v>524.0</v>
+        <v>522.0</v>
       </c>
       <c r="G120" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="48">
   <si>
     <t>Area</t>
   </si>
@@ -1846,7 +1846,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C64" t="s">
         <v>15</v>
@@ -1858,7 +1858,7 @@
         <v>40</v>
       </c>
       <c r="F64" t="n">
-        <v>1.0</v>
+        <v>35.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1872,7 +1872,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C65" t="s">
         <v>15</v>
@@ -1881,10 +1881,10 @@
         <v>27</v>
       </c>
       <c r="E65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F65" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1907,10 +1907,10 @@
         <v>27</v>
       </c>
       <c r="E66" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F66" t="n">
-        <v>34.0</v>
+        <v>67.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1930,16 +1930,16 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E67" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F67" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H67" t="n">
         <v>0.0</v>
@@ -1956,16 +1956,16 @@
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E68" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F68" t="n">
-        <v>65.0</v>
+        <v>18.0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1985,10 +1985,10 @@
         <v>28</v>
       </c>
       <c r="E69" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="G69" t="n">
         <v>1.0</v>
@@ -2011,7 +2011,7 @@
         <v>28</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F70" t="n">
         <v>18.0</v>
@@ -2037,16 +2037,16 @@
         <v>28</v>
       </c>
       <c r="E71" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F71" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="G71" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="72">
@@ -2054,19 +2054,19 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C72" t="s">
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E72" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F72" t="n">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="G72" t="n">
         <v>1.0</v>
@@ -2080,25 +2080,25 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C73" t="s">
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E73" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F73" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -2115,13 +2115,13 @@
         <v>29</v>
       </c>
       <c r="E74" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F74" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="G74" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2141,10 +2141,10 @@
         <v>29</v>
       </c>
       <c r="E75" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F75" t="n">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -2158,7 +2158,7 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C76" t="s">
         <v>15</v>
@@ -2167,13 +2167,13 @@
         <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F76" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2184,7 +2184,7 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C77" t="s">
         <v>15</v>
@@ -2193,13 +2193,13 @@
         <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F77" t="n">
-        <v>19.0</v>
+        <v>1.0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2219,13 +2219,13 @@
         <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G78" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2245,13 +2245,13 @@
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F79" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G79" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2262,7 +2262,7 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C80" t="s">
         <v>15</v>
@@ -2274,10 +2274,10 @@
         <v>42</v>
       </c>
       <c r="F80" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2288,7 +2288,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C81" t="s">
         <v>15</v>
@@ -2297,10 +2297,10 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F81" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2323,13 +2323,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F82" t="n">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="G82" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2346,16 +2346,16 @@
         <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E83" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F83" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2372,19 +2372,19 @@
         <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E84" t="s">
         <v>43</v>
       </c>
       <c r="F84" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="85">
@@ -2401,16 +2401,16 @@
         <v>30</v>
       </c>
       <c r="E85" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G85" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="86">
@@ -2427,16 +2427,16 @@
         <v>30</v>
       </c>
       <c r="E86" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F86" t="n">
-        <v>9.0</v>
+        <v>42.0</v>
       </c>
       <c r="G86" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H86" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="87">
@@ -2453,16 +2453,16 @@
         <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F87" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
       </c>
       <c r="H87" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="88">
@@ -2470,25 +2470,25 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E88" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F88" t="n">
-        <v>42.0</v>
+        <v>11.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
       </c>
       <c r="H88" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="89">
@@ -2496,25 +2496,25 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F89" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -2522,7 +2522,7 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C90" t="s">
         <v>16</v>
@@ -2531,13 +2531,13 @@
         <v>31</v>
       </c>
       <c r="E90" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F90" t="n">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H90" t="n">
         <v>0.0</v>
@@ -2548,7 +2548,7 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C91" t="s">
         <v>16</v>
@@ -2557,10 +2557,10 @@
         <v>31</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F91" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2574,7 +2574,7 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C92" t="s">
         <v>16</v>
@@ -2600,7 +2600,7 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
         <v>16</v>
@@ -2612,10 +2612,10 @@
         <v>42</v>
       </c>
       <c r="F93" t="n">
-        <v>27.0</v>
+        <v>1.0</v>
       </c>
       <c r="G93" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -2626,7 +2626,7 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
         <v>16</v>
@@ -2635,7 +2635,7 @@
         <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F94" t="n">
         <v>1.0</v>
@@ -2652,7 +2652,7 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C95" t="s">
         <v>16</v>
@@ -2661,10 +2661,10 @@
         <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F95" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2678,7 +2678,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2690,10 +2690,10 @@
         <v>42</v>
       </c>
       <c r="F96" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G96" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2704,7 +2704,7 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C97" t="s">
         <v>16</v>
@@ -2716,7 +2716,7 @@
         <v>43</v>
       </c>
       <c r="F97" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2730,25 +2730,25 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C98" t="s">
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E98" t="s">
         <v>42</v>
       </c>
       <c r="F98" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="99">
@@ -2756,19 +2756,19 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C99" t="s">
         <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E99" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F99" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2791,13 +2791,13 @@
         <v>32</v>
       </c>
       <c r="E100" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F100" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G100" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2808,7 +2808,7 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C101" t="s">
         <v>16</v>
@@ -2820,10 +2820,10 @@
         <v>42</v>
       </c>
       <c r="F101" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G101" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2834,7 +2834,7 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C102" t="s">
         <v>16</v>
@@ -2843,7 +2843,7 @@
         <v>32</v>
       </c>
       <c r="E102" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F102" t="n">
         <v>1.0</v>
@@ -2860,7 +2860,7 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
@@ -2872,7 +2872,7 @@
         <v>42</v>
       </c>
       <c r="F103" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2886,7 +2886,7 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C104" t="s">
         <v>16</v>
@@ -2895,13 +2895,13 @@
         <v>32</v>
       </c>
       <c r="E104" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F104" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H104" t="n">
         <v>0.0</v>
@@ -2912,7 +2912,7 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C105" t="s">
         <v>16</v>
@@ -2924,10 +2924,10 @@
         <v>40</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H105" t="n">
         <v>0.0</v>
@@ -2938,7 +2938,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C106" t="s">
         <v>16</v>
@@ -2950,13 +2950,13 @@
         <v>42</v>
       </c>
       <c r="F106" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H106" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -2973,13 +2973,13 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="G107" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2990,22 +2990,22 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E108" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F108" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G108" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3016,22 +3016,22 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
       </c>
       <c r="D109" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E109" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F109" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G109" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3042,22 +3042,22 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C110" t="s">
         <v>16</v>
       </c>
       <c r="D110" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E110" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="G110" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3077,13 +3077,13 @@
         <v>33</v>
       </c>
       <c r="E111" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3094,7 +3094,7 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C112" t="s">
         <v>16</v>
@@ -3103,13 +3103,13 @@
         <v>33</v>
       </c>
       <c r="E112" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G112" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3120,7 +3120,7 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C113" t="s">
         <v>16</v>
@@ -3129,7 +3129,7 @@
         <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F113" t="n">
         <v>1.0</v>
@@ -3155,13 +3155,13 @@
         <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F114" t="n">
         <v>2.0</v>
       </c>
       <c r="G114" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3172,7 +3172,7 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C115" t="s">
         <v>16</v>
@@ -3181,16 +3181,16 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F115" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="116">
@@ -3198,7 +3198,7 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C116" t="s">
         <v>16</v>
@@ -3207,13 +3207,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F116" t="n">
-        <v>2.0</v>
+        <v>86.0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3233,16 +3233,16 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
       <c r="G117" t="n">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="H117" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="118">
@@ -3259,16 +3259,16 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>88.0</v>
+        <v>514.0</v>
       </c>
       <c r="G118" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="119">
@@ -3285,13 +3285,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F119" t="n">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3308,19 +3308,19 @@
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E120" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F120" t="n">
-        <v>522.0</v>
+        <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H120" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="121">
@@ -3334,16 +3334,16 @@
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E121" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F121" t="n">
         <v>0.0</v>
       </c>
       <c r="G121" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3363,13 +3363,13 @@
         <v>34</v>
       </c>
       <c r="E122" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F122" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G122" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3389,13 +3389,13 @@
         <v>34</v>
       </c>
       <c r="E123" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="G123" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3412,16 +3412,16 @@
         <v>16</v>
       </c>
       <c r="D124" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E124" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F124" t="n">
         <v>7.0</v>
       </c>
       <c r="G124" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3438,19 +3438,19 @@
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E125" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F125" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="G125" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="126">
@@ -3467,10 +3467,10 @@
         <v>35</v>
       </c>
       <c r="E126" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F126" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G126" t="n">
         <v>0.0</v>
@@ -3484,25 +3484,25 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C127" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D127" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E127" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F127" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H127" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="128">
@@ -3510,22 +3510,22 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C128" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D128" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E128" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F128" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3545,7 +3545,7 @@
         <v>36</v>
       </c>
       <c r="E129" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F129" t="n">
         <v>0.0</v>
@@ -3571,13 +3571,13 @@
         <v>36</v>
       </c>
       <c r="E130" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F130" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G130" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3588,7 +3588,7 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C131" t="s">
         <v>17</v>
@@ -3597,13 +3597,13 @@
         <v>36</v>
       </c>
       <c r="E131" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G131" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>
@@ -3614,7 +3614,7 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C132" t="s">
         <v>17</v>
@@ -3623,13 +3623,13 @@
         <v>36</v>
       </c>
       <c r="E132" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F132" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3649,13 +3649,13 @@
         <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F133" t="n">
         <v>2.0</v>
       </c>
       <c r="G133" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3675,13 +3675,13 @@
         <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G134" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3692,7 +3692,7 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C135" t="s">
         <v>17</v>
@@ -3701,13 +3701,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F135" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3718,7 +3718,7 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C136" t="s">
         <v>17</v>
@@ -3727,10 +3727,10 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F136" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G136" t="n">
         <v>0.0</v>
@@ -3753,13 +3753,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F137" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G137" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3779,10 +3779,10 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F138" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -3796,22 +3796,22 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E139" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F139" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3822,22 +3822,22 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E140" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F140" t="n">
         <v>5.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3857,13 +3857,13 @@
         <v>37</v>
       </c>
       <c r="E141" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F141" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G141" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3883,13 +3883,13 @@
         <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F142" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G142" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3909,13 +3909,13 @@
         <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G143" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3935,10 +3935,10 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F144" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>
@@ -3952,19 +3952,19 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E145" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F145" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3978,22 +3978,22 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E146" t="s">
         <v>43</v>
       </c>
       <c r="F146" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4004,19 +4004,19 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E147" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F147" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -4030,7 +4030,7 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -4039,13 +4039,13 @@
         <v>39</v>
       </c>
       <c r="E148" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G148" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4056,7 +4056,7 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
@@ -4065,13 +4065,13 @@
         <v>39</v>
       </c>
       <c r="E149" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F149" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4082,7 +4082,7 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
@@ -4091,13 +4091,13 @@
         <v>39</v>
       </c>
       <c r="E150" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F150" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G150" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G150" t="n">
-        <v>0.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4117,13 +4117,13 @@
         <v>39</v>
       </c>
       <c r="E151" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F151" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G151" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4143,13 +4143,13 @@
         <v>39</v>
       </c>
       <c r="E152" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F152" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G152" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4169,10 +4169,10 @@
         <v>39</v>
       </c>
       <c r="E153" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F153" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G153" t="n">
         <v>1.0</v>
@@ -4195,67 +4195,15 @@
         <v>39</v>
       </c>
       <c r="E154" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F154" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>8</v>
-      </c>
-      <c r="B155" t="s">
-        <v>9</v>
-      </c>
-      <c r="C155" t="s">
-        <v>17</v>
-      </c>
-      <c r="D155" t="s">
-        <v>39</v>
-      </c>
-      <c r="E155" t="s">
-        <v>43</v>
-      </c>
-      <c r="F155" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>8</v>
-      </c>
-      <c r="B156" t="s">
-        <v>9</v>
-      </c>
-      <c r="C156" t="s">
-        <v>17</v>
-      </c>
-      <c r="D156" t="s">
-        <v>39</v>
-      </c>
-      <c r="E156" t="s">
-        <v>44</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H156" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3262,7 +3262,7 @@
         <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>514.0</v>
+        <v>513.0</v>
       </c>
       <c r="G118" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -2378,7 +2378,7 @@
         <v>43</v>
       </c>
       <c r="F84" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="G84" t="n">
         <v>2.0</v>
@@ -2482,7 +2482,7 @@
         <v>42</v>
       </c>
       <c r="F88" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2820,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="F101" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -948,7 +948,7 @@
         <v>42</v>
       </c>
       <c r="F29" t="n">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3262,7 +3262,7 @@
         <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>513.0</v>
+        <v>511.0</v>
       </c>
       <c r="G118" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -4042,7 +4042,7 @@
         <v>41</v>
       </c>
       <c r="F148" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1780,7 +1780,7 @@
         <v>40</v>
       </c>
       <c r="F61" t="n">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1832,7 +1832,7 @@
         <v>43</v>
       </c>
       <c r="F63" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -974,7 +974,7 @@
         <v>43</v>
       </c>
       <c r="F30" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -2430,7 +2430,7 @@
         <v>41</v>
       </c>
       <c r="F86" t="n">
-        <v>42.0</v>
+        <v>38.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -3938,7 +3938,7 @@
         <v>43</v>
       </c>
       <c r="F144" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1780,7 +1780,7 @@
         <v>40</v>
       </c>
       <c r="F61" t="n">
-        <v>38.0</v>
+        <v>37.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -2274,7 +2274,7 @@
         <v>42</v>
       </c>
       <c r="F80" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="G80" t="n">
         <v>1.0</v>
@@ -3262,7 +3262,7 @@
         <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>511.0</v>
+        <v>512.0</v>
       </c>
       <c r="G118" t="n">
         <v>7.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="48">
   <si>
     <t>Area</t>
   </si>
@@ -29,27 +29,27 @@
     <t>Orientamento produttivo</t>
   </si>
   <si>
+    <t>Semi brado</t>
+  </si>
+  <si>
     <t>Stabulato</t>
   </si>
   <si>
-    <t>Semi brado</t>
-  </si>
-  <si>
     <t>Non indicato</t>
   </si>
   <si>
     <t>Pl</t>
   </si>
   <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
     <t>LIM</t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
     <t>III</t>
   </si>
   <si>
@@ -134,19 +134,19 @@
     <t>PT</t>
   </si>
   <si>
+    <t>Non dpa</t>
+  </si>
+  <si>
+    <t>Familiare</t>
+  </si>
+  <si>
+    <t>Produzione da ingrasso</t>
+  </si>
+  <si>
+    <t>Struttura faunistica venatoria per cinghiali</t>
+  </si>
+  <si>
     <t>Da riproduzione</t>
-  </si>
-  <si>
-    <t>Familiare</t>
-  </si>
-  <si>
-    <t>Non dpa</t>
-  </si>
-  <si>
-    <t>Produzione da ingrasso</t>
-  </si>
-  <si>
-    <t>Struttura faunistica venatoria per cinghiali</t>
   </si>
   <si>
     <t>Collezione faunistica - giardino zoologico</t>
@@ -246,10 +246,10 @@
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H2" t="n">
         <v>0.0</v>
@@ -272,10 +272,10 @@
         <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H3" t="n">
         <v>0.0</v>
@@ -298,10 +298,10 @@
         <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H4" t="n">
         <v>0.0</v>
@@ -324,7 +324,7 @@
         <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -338,7 +338,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -347,10 +347,10 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G6" t="n">
         <v>1.0</v>
@@ -364,22 +364,22 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H7" t="n">
         <v>0.0</v>
@@ -390,22 +390,22 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H8" t="n">
         <v>0.0</v>
@@ -416,22 +416,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H9" t="n">
         <v>0.0</v>
@@ -448,16 +448,16 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0</v>
+        <v>30.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
@@ -474,10 +474,10 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>1.0</v>
@@ -494,7 +494,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -503,13 +503,13 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G12" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0</v>
       </c>
       <c r="H12" t="n">
         <v>0.0</v>
@@ -529,13 +529,13 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H13" t="n">
         <v>0.0</v>
@@ -555,13 +555,13 @@
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H14" t="n">
         <v>0.0</v>
@@ -584,10 +584,10 @@
         <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H15" t="n">
         <v>0.0</v>
@@ -598,7 +598,7 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
@@ -607,10 +607,10 @@
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" t="n">
-        <v>70.0</v>
+        <v>2.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -630,16 +630,16 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
         <v>40</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H17" t="n">
         <v>0.0</v>
@@ -656,16 +656,16 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H18" t="n">
         <v>0.0</v>
@@ -682,16 +682,16 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F19" t="n">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0</v>
+        <v>25.0</v>
       </c>
       <c r="H19" t="n">
         <v>0.0</v>
@@ -708,16 +708,16 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F20" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
       <c r="H20" t="n">
         <v>0.0</v>
@@ -734,16 +734,16 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0</v>
+        <v>70.0</v>
       </c>
       <c r="H21" t="n">
         <v>0.0</v>
@@ -754,7 +754,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
         <v>13</v>
@@ -763,13 +763,13 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H22" t="n">
         <v>0.0</v>
@@ -780,7 +780,7 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
@@ -789,13 +789,13 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>27.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H23" t="n">
         <v>0.0</v>
@@ -812,16 +812,16 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H24" t="n">
         <v>0.0</v>
@@ -838,16 +838,16 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F25" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H25" t="n">
         <v>0.0</v>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F26" t="n">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -884,22 +884,22 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F27" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -910,22 +910,22 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>2.0</v>
+        <v>26.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -936,7 +936,7 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
         <v>13</v>
@@ -945,13 +945,13 @@
         <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F29" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" t="n">
         <v>0.0</v>
@@ -962,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
@@ -971,13 +971,13 @@
         <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F30" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H30" t="n">
         <v>0.0</v>
@@ -997,13 +997,13 @@
         <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F31" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="H31" t="n">
         <v>0.0</v>
@@ -1014,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
@@ -1023,13 +1023,13 @@
         <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F32" t="n">
         <v>2.0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H32" t="n">
         <v>0.0</v>
@@ -1040,7 +1040,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
@@ -1052,7 +1052,7 @@
         <v>43</v>
       </c>
       <c r="F33" t="n">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1072,16 +1072,16 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
         <v>40</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G34" t="n">
-        <v>3.0</v>
+        <v>28.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>
@@ -1098,16 +1098,16 @@
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E35" t="s">
         <v>42</v>
       </c>
       <c r="F35" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="H35" t="n">
         <v>0.0</v>
@@ -1118,22 +1118,22 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G36" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H36" t="n">
         <v>0.0</v>
@@ -1144,22 +1144,22 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>
       </c>
       <c r="G37" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1176,16 +1176,16 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F38" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G38" t="n">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1196,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
@@ -1205,13 +1205,13 @@
         <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F39" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G39" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1.0</v>
       </c>
       <c r="H39" t="n">
         <v>0.0</v>
@@ -1222,7 +1222,7 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C40" t="s">
         <v>13</v>
@@ -1231,13 +1231,13 @@
         <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>
@@ -1257,13 +1257,13 @@
         <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F41" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G41" t="n">
         <v>13.0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1.0</v>
       </c>
       <c r="H41" t="n">
         <v>0.0</v>
@@ -1283,10 +1283,10 @@
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F42" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1300,7 +1300,7 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -1309,13 +1309,13 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F43" t="n">
-        <v>115.0</v>
+        <v>3.0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1326,22 +1326,22 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F44" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G44" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>4.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1352,22 +1352,22 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F45" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
       <c r="G45" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1381,19 +1381,19 @@
         <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
         <v>44</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G46" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1407,19 +1407,19 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F47" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1433,19 +1433,19 @@
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>1.0</v>
+        <v>115.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1456,16 +1456,16 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E49" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F49" t="n">
         <v>4.0</v>
@@ -1482,22 +1482,22 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1508,22 +1508,22 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G51" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1534,22 +1534,22 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F52" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1566,13 +1566,13 @@
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F53" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1586,22 +1586,22 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G54" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1612,19 +1612,19 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F55" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1638,19 +1638,19 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1664,13 +1664,13 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
         <v>44</v>
@@ -1679,7 +1679,7 @@
         <v>0.0</v>
       </c>
       <c r="G57" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1699,13 +1699,13 @@
         <v>25</v>
       </c>
       <c r="E58" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F58" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G58" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1728,10 +1728,10 @@
         <v>42</v>
       </c>
       <c r="F59" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H59" t="n">
         <v>0.0</v>
@@ -1742,7 +1742,7 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -1754,7 +1754,7 @@
         <v>43</v>
       </c>
       <c r="F60" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1768,25 +1768,25 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F61" t="n">
-        <v>37.0</v>
+        <v>0.0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H61" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62">
@@ -1794,25 +1794,25 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F62" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H62" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -1820,25 +1820,25 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E63" t="s">
         <v>43</v>
       </c>
       <c r="F63" t="n">
-        <v>172.0</v>
+        <v>1.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
       </c>
       <c r="H63" t="n">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
@@ -1846,22 +1846,22 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F64" t="n">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H64" t="n">
         <v>0.0</v>
@@ -1872,22 +1872,22 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F65" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H65" t="n">
         <v>0.0</v>
@@ -1898,25 +1898,25 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E66" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F66" t="n">
-        <v>67.0</v>
+        <v>0.0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0</v>
+        <v>37.0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="67">
@@ -1924,25 +1924,25 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C67" t="s">
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
       </c>
       <c r="G67" t="n">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="68">
@@ -1950,25 +1950,25 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C68" t="s">
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F68" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>1.0</v>
+        <v>172.0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="69">
@@ -1976,22 +1976,22 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C69" t="s">
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E69" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F69" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>1.0</v>
+        <v>35.0</v>
       </c>
       <c r="H69" t="n">
         <v>0.0</v>
@@ -2002,22 +2002,22 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E70" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F70" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H70" t="n">
         <v>0.0</v>
@@ -2028,25 +2028,25 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C71" t="s">
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F71" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0</v>
+        <v>67.0</v>
       </c>
       <c r="H71" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -2054,22 +2054,22 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C72" t="s">
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E72" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F72" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G72" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2080,22 +2080,22 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C73" t="s">
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E73" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F73" t="n">
         <v>1.0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2106,22 +2106,22 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C74" t="s">
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E74" t="s">
         <v>40</v>
       </c>
       <c r="F74" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2132,22 +2132,22 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C75" t="s">
         <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F75" t="n">
-        <v>19.0</v>
+        <v>1.0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2164,19 +2164,19 @@
         <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F76" t="n">
         <v>0.0</v>
       </c>
       <c r="G76" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="77">
@@ -2184,7 +2184,7 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C77" t="s">
         <v>15</v>
@@ -2199,7 +2199,7 @@
         <v>1.0</v>
       </c>
       <c r="G77" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2210,7 +2210,7 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
@@ -2219,13 +2219,13 @@
         <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F78" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2236,7 +2236,7 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
@@ -2245,13 +2245,13 @@
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F79" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2274,10 +2274,10 @@
         <v>42</v>
       </c>
       <c r="F80" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2288,7 +2288,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
         <v>15</v>
@@ -2297,10 +2297,10 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F81" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2314,7 +2314,7 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C82" t="s">
         <v>15</v>
@@ -2323,13 +2323,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F82" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2340,22 +2340,22 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C83" t="s">
         <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F83" t="n">
         <v>0.0</v>
       </c>
       <c r="G83" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2366,25 +2366,25 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C84" t="s">
         <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F84" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H84" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="85">
@@ -2392,25 +2392,25 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E85" t="s">
         <v>40</v>
       </c>
       <c r="F85" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H85" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="86">
@@ -2418,25 +2418,25 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F86" t="n">
-        <v>38.0</v>
+        <v>0.0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H86" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="87">
@@ -2444,25 +2444,25 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E87" t="s">
         <v>42</v>
       </c>
       <c r="F87" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="H87" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="88">
@@ -2470,19 +2470,19 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E88" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F88" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2496,25 +2496,25 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F89" t="n">
         <v>2.0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="90">
@@ -2525,22 +2525,22 @@
         <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F90" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="G90" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="91">
@@ -2551,22 +2551,22 @@
         <v>11</v>
       </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F91" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="92">
@@ -2577,22 +2577,22 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F92" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="H92" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="93">
@@ -2600,7 +2600,7 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C93" t="s">
         <v>16</v>
@@ -2609,13 +2609,13 @@
         <v>31</v>
       </c>
       <c r="E93" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G93" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -2626,7 +2626,7 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C94" t="s">
         <v>16</v>
@@ -2635,13 +2635,13 @@
         <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F94" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H94" t="n">
         <v>0.0</v>
@@ -2652,7 +2652,7 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C95" t="s">
         <v>16</v>
@@ -2664,10 +2664,10 @@
         <v>40</v>
       </c>
       <c r="F95" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2678,7 +2678,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2687,13 +2687,13 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F96" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2704,7 +2704,7 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C97" t="s">
         <v>16</v>
@@ -2713,13 +2713,13 @@
         <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F97" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2730,25 +2730,25 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C98" t="s">
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F98" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G98" t="n">
         <v>1.0</v>
       </c>
       <c r="H98" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="99">
@@ -2756,22 +2756,22 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C99" t="s">
         <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F99" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2782,22 +2782,22 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
       </c>
       <c r="D100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F100" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G100" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2814,16 +2814,16 @@
         <v>16</v>
       </c>
       <c r="D101" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F101" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2834,22 +2834,22 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
         <v>16</v>
       </c>
       <c r="D102" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F102" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2860,7 +2860,7 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
@@ -2869,13 +2869,13 @@
         <v>32</v>
       </c>
       <c r="E103" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F103" t="n">
         <v>1.0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H103" t="n">
         <v>1.0</v>
@@ -2895,7 +2895,7 @@
         <v>32</v>
       </c>
       <c r="E104" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
@@ -2921,13 +2921,13 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F105" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G105" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H105" t="n">
         <v>0.0</v>
@@ -2938,7 +2938,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C106" t="s">
         <v>16</v>
@@ -2947,13 +2947,13 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F106" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G106" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -2964,7 +2964,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C107" t="s">
         <v>16</v>
@@ -2973,13 +2973,13 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F107" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2990,16 +2990,16 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F108" t="n">
         <v>0.0</v>
@@ -3008,7 +3008,7 @@
         <v>1.0</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="109">
@@ -3016,22 +3016,22 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
       </c>
       <c r="D109" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G109" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3042,22 +3042,22 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C110" t="s">
         <v>16</v>
       </c>
       <c r="D110" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G110" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3068,22 +3068,22 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C111" t="s">
         <v>16</v>
       </c>
       <c r="D111" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F111" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3100,16 +3100,16 @@
         <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F112" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G112" t="n">
-        <v>1.0</v>
+        <v>18.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3120,7 +3120,7 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C113" t="s">
         <v>16</v>
@@ -3129,13 +3129,13 @@
         <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F113" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3146,7 +3146,7 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C114" t="s">
         <v>16</v>
@@ -3155,13 +3155,13 @@
         <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F114" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3181,16 +3181,16 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G115" t="n">
-        <v>1.0</v>
+        <v>36.0</v>
       </c>
       <c r="H115" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="116">
@@ -3207,13 +3207,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F116" t="n">
-        <v>86.0</v>
+        <v>2.0</v>
       </c>
       <c r="G116" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3224,7 +3224,7 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C117" t="s">
         <v>16</v>
@@ -3233,13 +3233,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F117" t="n">
-        <v>26.0</v>
+        <v>1.0</v>
       </c>
       <c r="G117" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3250,7 +3250,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C118" t="s">
         <v>16</v>
@@ -3259,16 +3259,16 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F118" t="n">
-        <v>512.0</v>
+        <v>1.0</v>
       </c>
       <c r="G118" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H118" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -3276,7 +3276,7 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C119" t="s">
         <v>16</v>
@@ -3285,13 +3285,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F119" t="n">
         <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3302,22 +3302,22 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C120" t="s">
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F120" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G120" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3328,25 +3328,25 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C121" t="s">
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G121" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="122">
@@ -3354,22 +3354,22 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C122" t="s">
         <v>16</v>
       </c>
       <c r="D122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F122" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G122" t="n">
-        <v>2.0</v>
+        <v>79.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3380,22 +3380,22 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C123" t="s">
         <v>16</v>
       </c>
       <c r="D123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E123" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F123" t="n">
         <v>12.0</v>
       </c>
       <c r="G123" t="n">
-        <v>2.0</v>
+        <v>25.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3406,25 +3406,25 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C124" t="s">
         <v>16</v>
       </c>
       <c r="D124" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F124" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0</v>
+        <v>485.0</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="125">
@@ -3432,25 +3432,25 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C125" t="s">
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F125" t="n">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="G125" t="n">
         <v>0.0</v>
       </c>
       <c r="H125" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="126">
@@ -3458,22 +3458,22 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C126" t="s">
         <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E126" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F126" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3484,22 +3484,22 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C127" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D127" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E127" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G127" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3510,22 +3510,22 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C128" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F128" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G128" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3536,22 +3536,22 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C129" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D129" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G129" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3562,22 +3562,22 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C130" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D130" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E130" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F130" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3591,22 +3591,22 @@
         <v>11</v>
       </c>
       <c r="C131" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D131" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E131" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F131" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G131" t="n">
-        <v>4.0</v>
+        <v>16.0</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="132">
@@ -3617,19 +3617,19 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E132" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F132" t="n">
         <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3640,7 +3640,7 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -3655,7 +3655,7 @@
         <v>2.0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3666,7 +3666,7 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C134" t="s">
         <v>17</v>
@@ -3678,7 +3678,7 @@
         <v>43</v>
       </c>
       <c r="F134" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G134" t="n">
         <v>0.0</v>
@@ -3701,13 +3701,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F135" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G135" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3727,13 +3727,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F136" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3744,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -3753,13 +3753,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F137" t="n">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3770,7 +3770,7 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C138" t="s">
         <v>17</v>
@@ -3779,13 +3779,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F138" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3796,22 +3796,22 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F139" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G139" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3822,22 +3822,22 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F140" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G140" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3848,22 +3848,22 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F141" t="n">
         <v>0.0</v>
       </c>
       <c r="G141" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3880,16 +3880,16 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F142" t="n">
         <v>1.0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3906,16 +3906,16 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E143" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F143" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3926,7 +3926,7 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3935,13 +3935,13 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F144" t="n">
         <v>3.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3952,22 +3952,22 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F145" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3984,16 +3984,16 @@
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E146" t="s">
         <v>43</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G146" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4010,16 +4010,16 @@
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F147" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4030,22 +4030,22 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E148" t="s">
         <v>41</v>
       </c>
       <c r="F148" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4056,19 +4056,19 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F149" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G149" t="n">
         <v>3.0</v>
@@ -4088,7 +4088,7 @@
         <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E150" t="s">
         <v>45</v>
@@ -4097,7 +4097,7 @@
         <v>1.0</v>
       </c>
       <c r="G150" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4114,16 +4114,16 @@
         <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E151" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F151" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G151" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4140,16 +4140,16 @@
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E152" t="s">
         <v>41</v>
       </c>
       <c r="F152" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4166,13 +4166,13 @@
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F153" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="n">
         <v>1.0</v>
@@ -4192,18 +4192,304 @@
         <v>17</v>
       </c>
       <c r="D154" t="s">
+        <v>38</v>
+      </c>
+      <c r="E154" t="s">
+        <v>43</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>38</v>
+      </c>
+      <c r="E155" t="s">
+        <v>44</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>8</v>
+      </c>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" t="s">
+        <v>38</v>
+      </c>
+      <c r="E156" t="s">
+        <v>40</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
         <v>39</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E157" t="s">
+        <v>47</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" t="s">
+        <v>39</v>
+      </c>
+      <c r="E158" t="s">
+        <v>41</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>8</v>
+      </c>
+      <c r="B159" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" t="s">
+        <v>39</v>
+      </c>
+      <c r="E159" t="s">
+        <v>42</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>8</v>
+      </c>
+      <c r="B160" t="s">
+        <v>10</v>
+      </c>
+      <c r="C160" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" t="s">
+        <v>39</v>
+      </c>
+      <c r="E160" t="s">
+        <v>47</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" t="s">
+        <v>10</v>
+      </c>
+      <c r="C161" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" t="s">
+        <v>39</v>
+      </c>
+      <c r="E161" t="s">
+        <v>45</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" t="s">
+        <v>10</v>
+      </c>
+      <c r="C162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" t="s">
+        <v>39</v>
+      </c>
+      <c r="E162" t="s">
         <v>44</v>
       </c>
-      <c r="F154" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G154" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H154" t="n">
+      <c r="F162" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>8</v>
+      </c>
+      <c r="B163" t="s">
+        <v>10</v>
+      </c>
+      <c r="C163" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" t="s">
+        <v>39</v>
+      </c>
+      <c r="E163" t="s">
+        <v>41</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G163" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>8</v>
+      </c>
+      <c r="B164" t="s">
+        <v>10</v>
+      </c>
+      <c r="C164" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" t="s">
+        <v>39</v>
+      </c>
+      <c r="E164" t="s">
+        <v>42</v>
+      </c>
+      <c r="F164" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165" t="s">
+        <v>10</v>
+      </c>
+      <c r="C165" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" t="s">
+        <v>39</v>
+      </c>
+      <c r="E165" t="s">
+        <v>43</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H165" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1081,7 +1081,7 @@
         <v>0.0</v>
       </c>
       <c r="G34" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3421,7 +3421,7 @@
         <v>4.0</v>
       </c>
       <c r="G124" t="n">
-        <v>485.0</v>
+        <v>484.0</v>
       </c>
       <c r="H124" t="n">
         <v>1.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -2277,7 +2277,7 @@
         <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2563,7 +2563,7 @@
         <v>0.0</v>
       </c>
       <c r="G91" t="n">
-        <v>38.0</v>
+        <v>36.0</v>
       </c>
       <c r="H91" t="n">
         <v>3.0</v>
@@ -2589,7 +2589,7 @@
         <v>0.0</v>
       </c>
       <c r="G92" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="H92" t="n">
         <v>2.0</v>
@@ -3421,7 +3421,7 @@
         <v>4.0</v>
       </c>
       <c r="G124" t="n">
-        <v>484.0</v>
+        <v>485.0</v>
       </c>
       <c r="H124" t="n">
         <v>1.0</v>
@@ -3655,7 +3655,7 @@
         <v>2.0</v>
       </c>
       <c r="G133" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -457,7 +457,7 @@
         <v>1.0</v>
       </c>
       <c r="G10" t="n">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H22" t="n">
         <v>0.0</v>
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -1341,7 +1341,7 @@
         <v>1.0</v>
       </c>
       <c r="G44" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1445,7 +1445,7 @@
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>115.0</v>
+        <v>114.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1913,7 +1913,7 @@
         <v>0.0</v>
       </c>
       <c r="G66" t="n">
-        <v>37.0</v>
+        <v>36.0</v>
       </c>
       <c r="H66" t="n">
         <v>11.0</v>
@@ -1965,10 +1965,10 @@
         <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>172.0</v>
+        <v>168.0</v>
       </c>
       <c r="H68" t="n">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="69">
@@ -1991,7 +1991,7 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
       <c r="H69" t="n">
         <v>0.0</v>
@@ -2147,7 +2147,7 @@
         <v>1.0</v>
       </c>
       <c r="G75" t="n">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -3187,7 +3187,7 @@
         <v>3.0</v>
       </c>
       <c r="G115" t="n">
-        <v>36.0</v>
+        <v>33.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3369,7 +3369,7 @@
         <v>9.0</v>
       </c>
       <c r="G122" t="n">
-        <v>79.0</v>
+        <v>78.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3421,7 +3421,7 @@
         <v>4.0</v>
       </c>
       <c r="G124" t="n">
-        <v>485.0</v>
+        <v>472.0</v>
       </c>
       <c r="H124" t="n">
         <v>1.0</v>
@@ -3551,7 +3551,7 @@
         <v>2.0</v>
       </c>
       <c r="G129" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -4071,7 +4071,7 @@
         <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="48">
   <si>
     <t>Area</t>
   </si>
@@ -44,13 +44,13 @@
     <t>I</t>
   </si>
   <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>LIM</t>
+  </si>
+  <si>
     <t>II</t>
-  </si>
-  <si>
-    <t>LIM</t>
-  </si>
-  <si>
-    <t>III</t>
   </si>
   <si>
     <t>Emilia romagna</t>
@@ -598,7 +598,7 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
@@ -624,7 +624,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H17" t="n">
         <v>0.0</v>
@@ -650,7 +650,7 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
@@ -665,7 +665,7 @@
         <v>0.0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H18" t="n">
         <v>0.0</v>
@@ -676,7 +676,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
@@ -685,13 +685,13 @@
         <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G19" t="n">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
       <c r="H19" t="n">
         <v>0.0</v>
@@ -702,7 +702,7 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
@@ -711,13 +711,13 @@
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
       </c>
       <c r="G20" t="n">
-        <v>30.0</v>
+        <v>1.0</v>
       </c>
       <c r="H20" t="n">
         <v>0.0</v>
@@ -737,13 +737,13 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G21" t="n">
-        <v>70.0</v>
+        <v>25.0</v>
       </c>
       <c r="H21" t="n">
         <v>0.0</v>
@@ -754,22 +754,22 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
       <c r="H22" t="n">
         <v>0.0</v>
@@ -780,13 +780,13 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s">
         <v>42</v>
@@ -795,7 +795,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>9.0</v>
+        <v>70.0</v>
       </c>
       <c r="H23" t="n">
         <v>0.0</v>
@@ -806,7 +806,7 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
@@ -818,10 +818,10 @@
         <v>44</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="H24" t="n">
         <v>0.0</v>
@@ -832,7 +832,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -841,13 +841,13 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="H25" t="n">
         <v>0.0</v>
@@ -858,7 +858,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -867,13 +867,13 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -884,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
@@ -893,13 +893,13 @@
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -910,7 +910,7 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
@@ -919,13 +919,13 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -936,16 +936,16 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -962,22 +962,22 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>6.0</v>
+        <v>25.0</v>
       </c>
       <c r="H30" t="n">
         <v>0.0</v>
@@ -997,13 +997,13 @@
         <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
       </c>
       <c r="G31" t="n">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="H31" t="n">
         <v>0.0</v>
@@ -1014,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
@@ -1023,13 +1023,13 @@
         <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F32" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G32" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H32" t="n">
         <v>0.0</v>
@@ -1040,7 +1040,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
@@ -1049,13 +1049,13 @@
         <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F33" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="H33" t="n">
         <v>0.0</v>
@@ -1066,7 +1066,7 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -1075,13 +1075,13 @@
         <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G34" t="n">
-        <v>27.0</v>
+        <v>3.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>
@@ -1092,7 +1092,7 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
@@ -1101,13 +1101,13 @@
         <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G35" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="H35" t="n">
         <v>0.0</v>
@@ -1118,7 +1118,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
@@ -1127,13 +1127,13 @@
         <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F36" t="n">
         <v>0.0</v>
       </c>
       <c r="G36" t="n">
-        <v>3.0</v>
+        <v>27.0</v>
       </c>
       <c r="H36" t="n">
         <v>0.0</v>
@@ -1144,7 +1144,7 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
@@ -1153,13 +1153,13 @@
         <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>
       </c>
       <c r="G37" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1179,13 +1179,13 @@
         <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F38" t="n">
         <v>0.0</v>
       </c>
       <c r="G38" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1196,19 +1196,19 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F39" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1222,22 +1222,22 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
         <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F40" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G40" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>
@@ -1257,13 +1257,13 @@
         <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G41" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="H41" t="n">
         <v>0.0</v>
@@ -1283,13 +1283,13 @@
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F42" t="n">
         <v>1.0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1300,7 +1300,7 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -1309,13 +1309,13 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F43" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G43" t="n">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1326,7 +1326,7 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -1335,13 +1335,13 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1352,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
         <v>13</v>
@@ -1361,13 +1361,13 @@
         <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1378,7 +1378,7 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
@@ -1387,13 +1387,13 @@
         <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F46" t="n">
         <v>1.0</v>
       </c>
       <c r="G46" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1404,7 +1404,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
@@ -1419,7 +1419,7 @@
         <v>0.0</v>
       </c>
       <c r="G47" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1439,13 +1439,13 @@
         <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G48" t="n">
-        <v>114.0</v>
+        <v>13.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1456,22 +1456,22 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F49" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G49" t="n">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1482,22 +1482,22 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E50" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F50" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>22.0</v>
+        <v>114.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1508,7 +1508,7 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -1517,13 +1517,13 @@
         <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F51" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1534,7 +1534,7 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
@@ -1543,13 +1543,13 @@
         <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G52" t="n">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1560,16 +1560,16 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F53" t="n">
         <v>1.0</v>
@@ -1586,22 +1586,22 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E54" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F54" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G54" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1612,7 +1612,7 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -1621,7 +1621,7 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F55" t="n">
         <v>1.0</v>
@@ -1638,7 +1638,7 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -1647,13 +1647,13 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F56" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H56" t="n">
         <v>0.0</v>
@@ -1664,7 +1664,7 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -1673,13 +1673,13 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G57" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1690,22 +1690,22 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G58" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1716,22 +1716,22 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F59" t="n">
         <v>0.0</v>
       </c>
       <c r="G59" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H59" t="n">
         <v>0.0</v>
@@ -1742,7 +1742,7 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -1751,13 +1751,13 @@
         <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F60" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G60" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.0</v>
       </c>
       <c r="H60" t="n">
         <v>0.0</v>
@@ -1768,7 +1768,7 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -1777,13 +1777,13 @@
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F61" t="n">
         <v>0.0</v>
       </c>
       <c r="G61" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H61" t="n">
         <v>0.0</v>
@@ -1794,7 +1794,7 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -1803,13 +1803,13 @@
         <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G62" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1820,7 +1820,7 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
@@ -1829,13 +1829,13 @@
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F63" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H63" t="n">
         <v>0.0</v>
@@ -1846,7 +1846,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -1855,13 +1855,13 @@
         <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>0.0</v>
       </c>
       <c r="G64" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="H64" t="n">
         <v>0.0</v>
@@ -1881,13 +1881,13 @@
         <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G65" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H65" t="n">
         <v>0.0</v>
@@ -1901,22 +1901,22 @@
         <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F66" t="n">
         <v>0.0</v>
       </c>
       <c r="G66" t="n">
-        <v>36.0</v>
+        <v>2.0</v>
       </c>
       <c r="H66" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1927,22 +1927,22 @@
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
       </c>
       <c r="G67" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
       <c r="H67" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -1959,16 +1959,16 @@
         <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F68" t="n">
         <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>168.0</v>
+        <v>36.0</v>
       </c>
       <c r="H68" t="n">
-        <v>33.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="69">
@@ -1982,19 +1982,19 @@
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F69" t="n">
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>34.0</v>
+        <v>16.0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="70">
@@ -2008,19 +2008,19 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F70" t="n">
         <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>3.0</v>
+        <v>168.0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="71">
@@ -2037,13 +2037,13 @@
         <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F71" t="n">
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>67.0</v>
+        <v>33.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -2060,16 +2060,16 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F72" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2086,16 +2086,16 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E73" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G73" t="n">
-        <v>18.0</v>
+        <v>68.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2115,13 +2115,13 @@
         <v>28</v>
       </c>
       <c r="E74" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F74" t="n">
         <v>1.0</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2141,13 +2141,13 @@
         <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F75" t="n">
         <v>1.0</v>
       </c>
       <c r="G75" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2167,16 +2167,16 @@
         <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G76" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H76" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -2184,22 +2184,22 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C77" t="s">
         <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F77" t="n">
         <v>1.0</v>
       </c>
       <c r="G77" t="n">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2210,25 +2210,25 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F78" t="n">
         <v>0.0</v>
       </c>
       <c r="G78" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="79">
@@ -2245,13 +2245,13 @@
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G79" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2271,13 +2271,13 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2288,7 +2288,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C81" t="s">
         <v>15</v>
@@ -2297,13 +2297,13 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F81" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2314,7 +2314,7 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C82" t="s">
         <v>15</v>
@@ -2323,13 +2323,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F82" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G82" t="n">
-        <v>1.0</v>
+        <v>18.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2340,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
         <v>15</v>
@@ -2349,13 +2349,13 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G83" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2366,7 +2366,7 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
         <v>15</v>
@@ -2375,13 +2375,13 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G84" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2392,7 +2392,7 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C85" t="s">
         <v>15</v>
@@ -2404,7 +2404,7 @@
         <v>40</v>
       </c>
       <c r="F85" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G85" t="n">
         <v>8.0</v>
@@ -2418,7 +2418,7 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
         <v>15</v>
@@ -2427,13 +2427,13 @@
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F86" t="n">
         <v>0.0</v>
       </c>
       <c r="G86" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2453,13 +2453,13 @@
         <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G87" t="n">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="H87" t="n">
         <v>0.0</v>
@@ -2476,16 +2476,16 @@
         <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F88" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2502,19 +2502,19 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E89" t="s">
         <v>42</v>
       </c>
       <c r="F89" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G89" t="n">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="H89" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -2531,16 +2531,16 @@
         <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G90" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H90" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="91">
@@ -2557,16 +2557,16 @@
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G91" t="n">
-        <v>36.0</v>
+        <v>8.0</v>
       </c>
       <c r="H91" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="92">
@@ -2583,16 +2583,16 @@
         <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F92" t="n">
         <v>0.0</v>
       </c>
       <c r="G92" t="n">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="H92" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="93">
@@ -2600,25 +2600,25 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F93" t="n">
         <v>0.0</v>
       </c>
       <c r="G93" t="n">
-        <v>10.0</v>
+        <v>36.0</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="94">
@@ -2626,25 +2626,25 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E94" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F94" t="n">
         <v>0.0</v>
       </c>
       <c r="G94" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="H94" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="95">
@@ -2652,7 +2652,7 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C95" t="s">
         <v>16</v>
@@ -2664,10 +2664,10 @@
         <v>40</v>
       </c>
       <c r="F95" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G95" t="n">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2678,7 +2678,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2687,13 +2687,13 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F96" t="n">
         <v>0.0</v>
       </c>
       <c r="G96" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2704,7 +2704,7 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
         <v>16</v>
@@ -2713,13 +2713,13 @@
         <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G97" t="n">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2739,10 +2739,10 @@
         <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F98" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G98" t="n">
         <v>1.0</v>
@@ -2771,7 +2771,7 @@
         <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2782,7 +2782,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2791,13 +2791,13 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G100" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2808,7 +2808,7 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C101" t="s">
         <v>16</v>
@@ -2817,13 +2817,13 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F101" t="n">
         <v>0.0</v>
       </c>
       <c r="G101" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2843,13 +2843,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2860,25 +2860,25 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E103" t="s">
         <v>40</v>
       </c>
       <c r="F103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G103" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="H103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -2886,22 +2886,22 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C104" t="s">
         <v>16</v>
       </c>
       <c r="D104" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
       </c>
       <c r="G104" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H104" t="n">
         <v>0.0</v>
@@ -2921,16 +2921,16 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G105" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="106">
@@ -2938,7 +2938,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C106" t="s">
         <v>16</v>
@@ -2947,7 +2947,7 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F106" t="n">
         <v>0.0</v>
@@ -2964,7 +2964,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C107" t="s">
         <v>16</v>
@@ -2973,13 +2973,13 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -3008,7 +3008,7 @@
         <v>1.0</v>
       </c>
       <c r="H108" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="109">
@@ -3016,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -3025,13 +3025,13 @@
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F109" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3042,7 +3042,7 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C110" t="s">
         <v>16</v>
@@ -3051,16 +3051,16 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F110" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G110" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="111">
@@ -3077,13 +3077,13 @@
         <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F111" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G111" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3103,13 +3103,13 @@
         <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F112" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G112" t="n">
-        <v>18.0</v>
+        <v>4.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3120,22 +3120,22 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C113" t="s">
         <v>16</v>
       </c>
       <c r="D113" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F113" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G113" t="n">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3146,22 +3146,22 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C114" t="s">
         <v>16</v>
       </c>
       <c r="D114" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F114" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G114" t="n">
-        <v>1.0</v>
+        <v>18.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3181,13 +3181,13 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F115" t="n">
         <v>3.0</v>
       </c>
       <c r="G115" t="n">
-        <v>33.0</v>
+        <v>7.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3207,13 +3207,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F116" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3224,7 +3224,7 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C117" t="s">
         <v>16</v>
@@ -3233,13 +3233,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F117" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3250,7 +3250,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C118" t="s">
         <v>16</v>
@@ -3259,13 +3259,13 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G118" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3276,7 +3276,7 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C119" t="s">
         <v>16</v>
@@ -3285,13 +3285,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G119" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3302,7 +3302,7 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C120" t="s">
         <v>16</v>
@@ -3311,13 +3311,13 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3328,7 +3328,7 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C121" t="s">
         <v>16</v>
@@ -3337,16 +3337,16 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F121" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H121" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="122">
@@ -3354,7 +3354,7 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C122" t="s">
         <v>16</v>
@@ -3363,13 +3363,13 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F122" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>78.0</v>
+        <v>2.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3389,16 +3389,16 @@
         <v>33</v>
       </c>
       <c r="E123" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F123" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G123" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="124">
@@ -3415,16 +3415,16 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F124" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="G124" t="n">
-        <v>472.0</v>
+        <v>78.0</v>
       </c>
       <c r="H124" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="125">
@@ -3441,13 +3441,13 @@
         <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F125" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3464,19 +3464,19 @@
         <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E126" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F126" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G126" t="n">
-        <v>1.0</v>
+        <v>472.0</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="127">
@@ -3490,13 +3490,13 @@
         <v>16</v>
       </c>
       <c r="D127" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F127" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G127" t="n">
         <v>0.0</v>
@@ -3519,13 +3519,13 @@
         <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F128" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G128" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3545,13 +3545,13 @@
         <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F129" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G129" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3568,13 +3568,13 @@
         <v>16</v>
       </c>
       <c r="D130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G130" t="n">
         <v>7.0</v>
@@ -3594,19 +3594,19 @@
         <v>16</v>
       </c>
       <c r="D131" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G131" t="n">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="H131" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="132">
@@ -3623,13 +3623,13 @@
         <v>35</v>
       </c>
       <c r="E132" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F132" t="n">
         <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3640,25 +3640,25 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C133" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D133" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E133" t="s">
         <v>40</v>
       </c>
       <c r="F133" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="134">
@@ -3666,22 +3666,22 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D134" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F134" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3701,13 +3701,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3727,13 +3727,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G136" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3744,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -3753,13 +3753,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F137" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G137" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3770,7 +3770,7 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C138" t="s">
         <v>17</v>
@@ -3779,13 +3779,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F138" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3796,7 +3796,7 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
@@ -3805,13 +3805,13 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F139" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3822,7 +3822,7 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
@@ -3831,13 +3831,13 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G140" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3848,7 +3848,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
@@ -3857,7 +3857,7 @@
         <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F141" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
@@ -3883,13 +3883,13 @@
         <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F142" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G142" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3900,7 +3900,7 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
@@ -3909,13 +3909,13 @@
         <v>36</v>
       </c>
       <c r="E143" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F143" t="n">
         <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3932,16 +3932,16 @@
         <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E144" t="s">
         <v>44</v>
       </c>
       <c r="F144" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G144" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3952,19 +3952,19 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E145" t="s">
         <v>40</v>
       </c>
       <c r="F145" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G145" t="n">
         <v>5.0</v>
@@ -3978,22 +3978,22 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E146" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F146" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4004,7 +4004,7 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -4013,13 +4013,13 @@
         <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G147" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4030,7 +4030,7 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -4039,13 +4039,13 @@
         <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G148" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4056,7 +4056,7 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
@@ -4065,13 +4065,13 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F149" t="n">
         <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4082,22 +4082,22 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F150" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4108,22 +4108,22 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E151" t="s">
         <v>44</v>
       </c>
       <c r="F151" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4134,22 +4134,22 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C152" t="s">
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E152" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F152" t="n">
         <v>1.0</v>
       </c>
       <c r="G152" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4160,22 +4160,22 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C153" t="s">
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E153" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F153" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G153" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4186,22 +4186,22 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C154" t="s">
         <v>17</v>
       </c>
       <c r="D154" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E154" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F154" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4212,7 +4212,7 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C155" t="s">
         <v>17</v>
@@ -4221,7 +4221,7 @@
         <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F155" t="n">
         <v>1.0</v>
@@ -4238,7 +4238,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
@@ -4247,13 +4247,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4270,16 +4270,16 @@
         <v>17</v>
       </c>
       <c r="D157" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F157" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G157" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4296,16 +4296,16 @@
         <v>17</v>
       </c>
       <c r="D158" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F158" t="n">
         <v>1.0</v>
       </c>
       <c r="G158" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4322,16 +4322,16 @@
         <v>17</v>
       </c>
       <c r="D159" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G159" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4342,16 +4342,16 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F160" t="n">
         <v>1.0</v>
@@ -4368,19 +4368,19 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
       </c>
       <c r="D161" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F161" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G161" t="n">
         <v>1.0</v>
@@ -4394,7 +4394,7 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
@@ -4403,13 +4403,13 @@
         <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F162" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G162" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4420,7 +4420,7 @@
         <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C163" t="s">
         <v>17</v>
@@ -4432,10 +4432,10 @@
         <v>41</v>
       </c>
       <c r="F163" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G163" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4446,7 +4446,7 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
@@ -4458,10 +4458,10 @@
         <v>42</v>
       </c>
       <c r="F164" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4481,15 +4481,145 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
+        <v>47</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>8</v>
+      </c>
+      <c r="B166" t="s">
+        <v>10</v>
+      </c>
+      <c r="C166" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" t="s">
+        <v>39</v>
+      </c>
+      <c r="E166" t="s">
+        <v>45</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" t="s">
+        <v>10</v>
+      </c>
+      <c r="C167" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167" t="s">
+        <v>39</v>
+      </c>
+      <c r="E167" t="s">
+        <v>44</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>8</v>
+      </c>
+      <c r="B168" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" t="s">
+        <v>39</v>
+      </c>
+      <c r="E168" t="s">
+        <v>41</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G168" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>8</v>
+      </c>
+      <c r="B169" t="s">
+        <v>10</v>
+      </c>
+      <c r="C169" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169" t="s">
+        <v>39</v>
+      </c>
+      <c r="E169" t="s">
+        <v>42</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>8</v>
+      </c>
+      <c r="B170" t="s">
+        <v>10</v>
+      </c>
+      <c r="C170" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" t="s">
+        <v>39</v>
+      </c>
+      <c r="E170" t="s">
         <v>43</v>
       </c>
-      <c r="F165" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H165" t="n">
+      <c r="F170" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H170" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -2173,7 +2173,7 @@
         <v>1.0</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2225,7 +2225,7 @@
         <v>0.0</v>
       </c>
       <c r="G78" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H78" t="n">
         <v>1.0</v>
@@ -2251,7 +2251,7 @@
         <v>1.0</v>
       </c>
       <c r="G79" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2277,7 +2277,7 @@
         <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -4279,7 +4279,7 @@
         <v>1.0</v>
       </c>
       <c r="G157" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3317,7 +3317,7 @@
         <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3369,7 +3369,7 @@
         <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -2433,7 +2433,7 @@
         <v>0.0</v>
       </c>
       <c r="G86" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3418,7 +3418,7 @@
         <v>44</v>
       </c>
       <c r="F124" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G124" t="n">
         <v>78.0</v>
@@ -3470,7 +3470,7 @@
         <v>42</v>
       </c>
       <c r="F126" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G126" t="n">
         <v>472.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3473,7 +3473,7 @@
         <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>472.0</v>
+        <v>471.0</v>
       </c>
       <c r="H126" t="n">
         <v>1.0</v>
@@ -3808,7 +3808,7 @@
         <v>40</v>
       </c>
       <c r="F139" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G139" t="n">
         <v>3.0</v>
@@ -4201,7 +4201,7 @@
         <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3473,7 +3473,7 @@
         <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>471.0</v>
+        <v>470.0</v>
       </c>
       <c r="H126" t="n">
         <v>1.0</v>
@@ -4201,7 +4201,7 @@
         <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -2043,7 +2043,7 @@
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -3473,7 +3473,7 @@
         <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>470.0</v>
+        <v>471.0</v>
       </c>
       <c r="H126" t="n">
         <v>1.0</v>
@@ -3577,7 +3577,7 @@
         <v>2.0</v>
       </c>
       <c r="G130" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -4042,10 +4042,10 @@
         <v>40</v>
       </c>
       <c r="F148" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G148" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4065,7 +4065,7 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F149" t="n">
         <v>0.0</v>
@@ -4513,7 +4513,7 @@
         <v>2.0</v>
       </c>
       <c r="G166" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4562,10 +4562,10 @@
         <v>41</v>
       </c>
       <c r="F168" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G168" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -2043,7 +2043,7 @@
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -3704,10 +3704,10 @@
         <v>40</v>
       </c>
       <c r="F135" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G135" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1237,7 +1237,7 @@
         <v>0.0</v>
       </c>
       <c r="G40" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>
@@ -3707,7 +3707,7 @@
         <v>3.0</v>
       </c>
       <c r="G135" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3759,7 +3759,7 @@
         <v>0.0</v>
       </c>
       <c r="G137" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -4406,10 +4406,10 @@
         <v>47</v>
       </c>
       <c r="F162" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G162" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G162" t="n">
-        <v>3.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="48">
   <si>
     <t>Area</t>
   </si>
@@ -1497,7 +1497,7 @@
         <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>114.0</v>
+        <v>113.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -2719,7 +2719,7 @@
         <v>3.0</v>
       </c>
       <c r="G97" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2739,7 +2739,7 @@
         <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F98" t="n">
         <v>0.0</v>
@@ -2765,13 +2765,13 @@
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F99" t="n">
         <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2782,7 +2782,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2791,13 +2791,13 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F100" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G100" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2817,10 +2817,10 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>
@@ -2834,7 +2834,7 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C102" t="s">
         <v>16</v>
@@ -2843,13 +2843,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2869,13 +2869,13 @@
         <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F103" t="n">
         <v>0.0</v>
       </c>
       <c r="G103" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="H103" t="n">
         <v>0.0</v>
@@ -2895,13 +2895,13 @@
         <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
       </c>
       <c r="G104" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="H104" t="n">
         <v>0.0</v>
@@ -2912,25 +2912,25 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C105" t="s">
         <v>16</v>
       </c>
       <c r="D105" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E105" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G105" t="n">
         <v>4.0</v>
       </c>
       <c r="H105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="106">
@@ -2947,16 +2947,16 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G106" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="107">
@@ -2973,13 +2973,13 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2990,7 +2990,7 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
@@ -2999,13 +2999,13 @@
         <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F108" t="n">
         <v>0.0</v>
       </c>
       <c r="G108" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3016,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -3025,7 +3025,7 @@
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F109" t="n">
         <v>0.0</v>
@@ -3051,7 +3051,7 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F110" t="n">
         <v>0.0</v>
@@ -3060,7 +3060,7 @@
         <v>1.0</v>
       </c>
       <c r="H110" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="111">
@@ -3068,7 +3068,7 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C111" t="s">
         <v>16</v>
@@ -3077,16 +3077,16 @@
         <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="112">
@@ -3103,13 +3103,13 @@
         <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F112" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G112" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3129,13 +3129,13 @@
         <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F113" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3155,13 +3155,13 @@
         <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F114" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G114" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3172,22 +3172,22 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C115" t="s">
         <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E115" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F115" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G115" t="n">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3207,13 +3207,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F116" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G116" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3233,13 +3233,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F117" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G117" t="n">
-        <v>33.0</v>
+        <v>1.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3259,13 +3259,13 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3276,7 +3276,7 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C119" t="s">
         <v>16</v>
@@ -3285,10 +3285,10 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G119" t="n">
         <v>0.0</v>
@@ -3311,13 +3311,13 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F120" t="n">
         <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3337,13 +3337,13 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G121" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3363,13 +3363,13 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F122" t="n">
         <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3380,7 +3380,7 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C123" t="s">
         <v>16</v>
@@ -3389,16 +3389,16 @@
         <v>33</v>
       </c>
       <c r="E123" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F123" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H123" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="124">
@@ -3415,16 +3415,16 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F124" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G124" t="n">
-        <v>78.0</v>
+        <v>0.0</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="125">
@@ -3441,13 +3441,13 @@
         <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F125" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G125" t="n">
-        <v>25.0</v>
+        <v>78.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3467,16 +3467,16 @@
         <v>33</v>
       </c>
       <c r="E126" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F126" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="G126" t="n">
-        <v>471.0</v>
+        <v>25.0</v>
       </c>
       <c r="H126" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="127">
@@ -3493,16 +3493,16 @@
         <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F127" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0</v>
+        <v>471.0</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="128">
@@ -3516,16 +3516,16 @@
         <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E128" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F128" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G128" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3545,13 +3545,13 @@
         <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F129" t="n">
         <v>1.0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3571,13 +3571,13 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F130" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G130" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3597,13 +3597,13 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F131" t="n">
         <v>2.0</v>
       </c>
       <c r="G131" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>
@@ -3620,16 +3620,16 @@
         <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E132" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G132" t="n">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3649,16 +3649,16 @@
         <v>35</v>
       </c>
       <c r="E133" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F133" t="n">
         <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>16.0</v>
+        <v>7.0</v>
       </c>
       <c r="H133" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="134">
@@ -3675,16 +3675,16 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F134" t="n">
         <v>0.0</v>
       </c>
       <c r="G134" t="n">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="135">
@@ -3692,22 +3692,22 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C135" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D135" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F135" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G135" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3727,13 +3727,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F136" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3753,13 +3753,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G137" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3779,13 +3779,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F138" t="n">
         <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3796,7 +3796,7 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
@@ -3805,13 +3805,13 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F139" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G139" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3831,13 +3831,13 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F140" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3857,13 +3857,13 @@
         <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G141" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3883,13 +3883,13 @@
         <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F142" t="n">
         <v>0.0</v>
       </c>
       <c r="G142" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3909,13 +3909,13 @@
         <v>36</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F143" t="n">
         <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3926,7 +3926,7 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3935,13 +3935,13 @@
         <v>36</v>
       </c>
       <c r="E144" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F144" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3952,7 +3952,7 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3961,13 +3961,13 @@
         <v>36</v>
       </c>
       <c r="E145" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F145" t="n">
         <v>1.0</v>
       </c>
       <c r="G145" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3987,13 +3987,13 @@
         <v>36</v>
       </c>
       <c r="E146" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G146" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4004,22 +4004,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E147" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F147" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4039,13 +4039,13 @@
         <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F148" t="n">
         <v>1.0</v>
       </c>
       <c r="G148" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4065,13 +4065,13 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4091,13 +4091,13 @@
         <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F150" t="n">
         <v>0.0</v>
       </c>
       <c r="G150" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4108,7 +4108,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4117,13 +4117,13 @@
         <v>37</v>
       </c>
       <c r="E151" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F151" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G151" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4143,13 +4143,13 @@
         <v>37</v>
       </c>
       <c r="E152" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F152" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4169,13 +4169,13 @@
         <v>37</v>
       </c>
       <c r="E153" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4195,7 +4195,7 @@
         <v>37</v>
       </c>
       <c r="E154" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F154" t="n">
         <v>0.0</v>
@@ -4212,22 +4212,22 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C155" t="s">
         <v>17</v>
       </c>
       <c r="D155" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E155" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F155" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4247,10 +4247,10 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F156" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G156" t="n">
         <v>0.0</v>
@@ -4273,13 +4273,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F157" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G157" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4299,13 +4299,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F158" t="n">
         <v>1.0</v>
       </c>
       <c r="G158" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4325,13 +4325,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F159" t="n">
         <v>1.0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4342,7 +4342,7 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
@@ -4351,7 +4351,7 @@
         <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F160" t="n">
         <v>1.0</v>
@@ -4377,13 +4377,13 @@
         <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G161" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4394,22 +4394,22 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E162" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F162" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G162" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4429,13 +4429,13 @@
         <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F163" t="n">
         <v>1.0</v>
       </c>
       <c r="G163" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4455,13 +4455,13 @@
         <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G164" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4472,7 +4472,7 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C165" t="s">
         <v>17</v>
@@ -4481,13 +4481,13 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F165" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4507,10 +4507,10 @@
         <v>39</v>
       </c>
       <c r="E166" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F166" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G166" t="n">
         <v>0.0</v>
@@ -4533,13 +4533,13 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F167" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G167" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>
@@ -4559,13 +4559,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F168" t="n">
         <v>1.0</v>
       </c>
       <c r="G168" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4585,13 +4585,13 @@
         <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F169" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4611,15 +4611,41 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
+        <v>42</v>
+      </c>
+      <c r="F170" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>8</v>
+      </c>
+      <c r="B171" t="s">
+        <v>10</v>
+      </c>
+      <c r="C171" t="s">
+        <v>17</v>
+      </c>
+      <c r="D171" t="s">
+        <v>39</v>
+      </c>
+      <c r="E171" t="s">
         <v>43</v>
       </c>
-      <c r="F170" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G170" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H170" t="n">
+      <c r="F171" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H171" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3499,7 +3499,7 @@
         <v>3.0</v>
       </c>
       <c r="G127" t="n">
-        <v>471.0</v>
+        <v>470.0</v>
       </c>
       <c r="H127" t="n">
         <v>1.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -457,7 +457,7 @@
         <v>1.0</v>
       </c>
       <c r="G10" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
@@ -821,7 +821,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H24" t="n">
         <v>0.0</v>
@@ -977,7 +977,7 @@
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="H30" t="n">
         <v>0.0</v>
@@ -1497,7 +1497,7 @@
         <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1965,7 +1965,7 @@
         <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="H68" t="n">
         <v>11.0</v>
@@ -2017,10 +2017,10 @@
         <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>168.0</v>
+        <v>172.0</v>
       </c>
       <c r="H70" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="71">
@@ -2043,7 +2043,7 @@
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -2199,7 +2199,7 @@
         <v>1.0</v>
       </c>
       <c r="G77" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -3265,7 +3265,7 @@
         <v>3.0</v>
       </c>
       <c r="G118" t="n">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3447,7 +3447,7 @@
         <v>10.0</v>
       </c>
       <c r="G125" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3499,7 +3499,7 @@
         <v>3.0</v>
       </c>
       <c r="G127" t="n">
-        <v>470.0</v>
+        <v>483.0</v>
       </c>
       <c r="H127" t="n">
         <v>1.0</v>
@@ -3629,7 +3629,7 @@
         <v>2.0</v>
       </c>
       <c r="G132" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -4461,7 +4461,7 @@
         <v>1.0</v>
       </c>
       <c r="G164" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4591,7 +4591,7 @@
         <v>1.0</v>
       </c>
       <c r="G169" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="48">
   <si>
     <t>Area</t>
   </si>
@@ -1445,7 +1445,7 @@
         <v>1.0</v>
       </c>
       <c r="G48" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1497,7 +1497,7 @@
         <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>114.0</v>
+        <v>113.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1968,7 +1968,7 @@
         <v>37.0</v>
       </c>
       <c r="H68" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="69">
@@ -2095,7 +2095,7 @@
         <v>0.0</v>
       </c>
       <c r="G73" t="n">
-        <v>68.0</v>
+        <v>66.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -3187,7 +3187,7 @@
         <v>2.0</v>
       </c>
       <c r="G115" t="n">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3447,7 +3447,7 @@
         <v>10.0</v>
       </c>
       <c r="G125" t="n">
-        <v>79.0</v>
+        <v>78.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3499,7 +3499,7 @@
         <v>3.0</v>
       </c>
       <c r="G127" t="n">
-        <v>483.0</v>
+        <v>478.0</v>
       </c>
       <c r="H127" t="n">
         <v>1.0</v>
@@ -3785,7 +3785,7 @@
         <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3987,13 +3987,13 @@
         <v>36</v>
       </c>
       <c r="E146" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F146" t="n">
         <v>1.0</v>
       </c>
       <c r="G146" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4013,13 +4013,13 @@
         <v>36</v>
       </c>
       <c r="E147" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G147" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4461,7 +4461,7 @@
         <v>1.0</v>
       </c>
       <c r="G164" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4481,13 +4481,13 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F165" t="n">
         <v>0.0</v>
       </c>
       <c r="G165" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4498,7 +4498,7 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
@@ -4507,13 +4507,13 @@
         <v>39</v>
       </c>
       <c r="E166" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F166" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4533,10 +4533,10 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F167" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -4559,13 +4559,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F168" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G168" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4585,13 +4585,13 @@
         <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F169" t="n">
         <v>1.0</v>
       </c>
       <c r="G169" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4611,13 +4611,13 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F170" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4637,15 +4637,41 @@
         <v>39</v>
       </c>
       <c r="E171" t="s">
+        <v>42</v>
+      </c>
+      <c r="F171" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" t="s">
+        <v>39</v>
+      </c>
+      <c r="E172" t="s">
         <v>43</v>
       </c>
-      <c r="F171" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G171" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H171" t="n">
+      <c r="F172" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H172" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -2043,7 +2043,7 @@
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -3499,7 +3499,7 @@
         <v>3.0</v>
       </c>
       <c r="G127" t="n">
-        <v>478.0</v>
+        <v>476.0</v>
       </c>
       <c r="H127" t="n">
         <v>1.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3990,7 +3990,7 @@
         <v>46</v>
       </c>
       <c r="F146" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -4016,7 +4016,7 @@
         <v>40</v>
       </c>
       <c r="F147" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
         <v>5.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -399,13 +399,13 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G8" t="n">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="H8" t="n">
         <v>0.0</v>
@@ -425,13 +425,13 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G9" t="n">
-        <v>9.0</v>
+        <v>30.0</v>
       </c>
       <c r="H9" t="n">
         <v>0.0</v>
@@ -451,13 +451,13 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
       </c>
       <c r="G10" t="n">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
@@ -477,13 +477,13 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H11" t="n">
         <v>0.0</v>
@@ -2043,7 +2043,7 @@
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1387,10 +1387,10 @@
         <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F46" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G46" t="n">
         <v>1.0</v>
@@ -1413,7 +1413,7 @@
         <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F47" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -1283,13 +1283,13 @@
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F42" t="n">
         <v>1.0</v>
       </c>
       <c r="G42" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1309,13 +1309,13 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F43" t="n">
         <v>1.0</v>
       </c>
       <c r="G43" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1335,13 +1335,13 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -4461,7 +4461,7 @@
         <v>1.0</v>
       </c>
       <c r="G164" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4487,7 +4487,7 @@
         <v>0.0</v>
       </c>
       <c r="G165" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -3473,7 +3473,7 @@
         <v>12.0</v>
       </c>
       <c r="G126" t="n">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -4019,7 +4019,7 @@
         <v>0.0</v>
       </c>
       <c r="G147" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="48">
   <si>
     <t>Area</t>
   </si>
@@ -1309,13 +1309,13 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F43" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1326,7 +1326,7 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -1335,13 +1335,13 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G44" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1361,13 +1361,13 @@
         <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F45" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G45" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1387,7 +1387,7 @@
         <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F46" t="n">
         <v>0.0</v>
@@ -1404,7 +1404,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
@@ -1413,13 +1413,13 @@
         <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G47" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1439,13 +1439,13 @@
         <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F48" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1465,13 +1465,13 @@
         <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F49" t="n">
         <v>0.0</v>
       </c>
       <c r="G49" t="n">
-        <v>16.0</v>
+        <v>113.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1482,22 +1482,22 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G50" t="n">
-        <v>113.0</v>
+        <v>2.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1517,13 +1517,13 @@
         <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F51" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G51" t="n">
-        <v>2.0</v>
+        <v>22.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1543,13 +1543,13 @@
         <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F52" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G52" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1569,13 +1569,13 @@
         <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F53" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H53" t="n">
         <v>0.0</v>
@@ -1592,16 +1592,16 @@
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G54" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1621,13 +1621,13 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F55" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1647,13 +1647,13 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F56" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G56" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H56" t="n">
         <v>0.0</v>
@@ -1673,10 +1673,10 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F57" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -1699,13 +1699,13 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F58" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1716,16 +1716,16 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F59" t="n">
         <v>0.0</v>
@@ -1751,13 +1751,13 @@
         <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F60" t="n">
         <v>0.0</v>
       </c>
       <c r="G60" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H60" t="n">
         <v>0.0</v>
@@ -1768,7 +1768,7 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -1777,13 +1777,13 @@
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G61" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H61" t="n">
         <v>0.0</v>
@@ -1803,13 +1803,13 @@
         <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F62" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1829,13 +1829,13 @@
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F63" t="n">
         <v>0.0</v>
       </c>
       <c r="G63" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="H63" t="n">
         <v>0.0</v>
@@ -1846,7 +1846,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -1855,13 +1855,13 @@
         <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G64" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H64" t="n">
         <v>0.0</v>
@@ -1881,13 +1881,13 @@
         <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F65" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H65" t="n">
         <v>0.0</v>
@@ -1907,13 +1907,13 @@
         <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F66" t="n">
         <v>0.0</v>
       </c>
       <c r="G66" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H66" t="n">
         <v>0.0</v>
@@ -1927,22 +1927,22 @@
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
       </c>
       <c r="G67" t="n">
-        <v>8.0</v>
+        <v>37.0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="68">
@@ -1959,16 +1959,16 @@
         <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F68" t="n">
         <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>37.0</v>
+        <v>16.0</v>
       </c>
       <c r="H68" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="69">
@@ -1985,16 +1985,16 @@
         <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F69" t="n">
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>16.0</v>
+        <v>172.0</v>
       </c>
       <c r="H69" t="n">
-        <v>3.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="70">
@@ -2008,19 +2008,19 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E70" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F70" t="n">
         <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>172.0</v>
+        <v>34.0</v>
       </c>
       <c r="H70" t="n">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="71">
@@ -2037,13 +2037,13 @@
         <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F71" t="n">
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>34.0</v>
+        <v>3.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -2063,13 +2063,13 @@
         <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F72" t="n">
         <v>0.0</v>
       </c>
       <c r="G72" t="n">
-        <v>3.0</v>
+        <v>66.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2086,16 +2086,16 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E73" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G73" t="n">
-        <v>66.0</v>
+        <v>0.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2115,13 +2115,13 @@
         <v>28</v>
       </c>
       <c r="E74" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F74" t="n">
         <v>1.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2141,13 +2141,13 @@
         <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F75" t="n">
         <v>1.0</v>
       </c>
       <c r="G75" t="n">
-        <v>18.0</v>
+        <v>11.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2167,13 +2167,13 @@
         <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F76" t="n">
         <v>1.0</v>
       </c>
       <c r="G76" t="n">
-        <v>11.0</v>
+        <v>18.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2193,16 +2193,16 @@
         <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F77" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G77" t="n">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="78">
@@ -2210,25 +2210,25 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G78" t="n">
         <v>7.0</v>
       </c>
       <c r="H78" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="79">
@@ -2245,13 +2245,13 @@
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F79" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G79" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2271,7 +2271,7 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
@@ -2297,13 +2297,13 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
         <v>0.0</v>
       </c>
       <c r="G81" t="n">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2314,7 +2314,7 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
         <v>15</v>
@@ -2323,13 +2323,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2349,13 +2349,13 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F83" t="n">
         <v>1.0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2375,13 +2375,13 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F84" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2401,13 +2401,13 @@
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F85" t="n">
         <v>0.0</v>
       </c>
       <c r="G85" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2418,7 +2418,7 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
         <v>15</v>
@@ -2427,13 +2427,13 @@
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G86" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2453,10 +2453,10 @@
         <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F87" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G87" t="n">
         <v>8.0</v>
@@ -2479,13 +2479,13 @@
         <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F88" t="n">
         <v>0.0</v>
       </c>
       <c r="G88" t="n">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2502,16 +2502,16 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G89" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="H89" t="n">
         <v>0.0</v>
@@ -2531,16 +2531,16 @@
         <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F90" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="91">
@@ -2557,16 +2557,16 @@
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F91" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G91" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="H91" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="92">
@@ -2583,16 +2583,16 @@
         <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F92" t="n">
         <v>0.0</v>
       </c>
       <c r="G92" t="n">
-        <v>5.0</v>
+        <v>36.0</v>
       </c>
       <c r="H92" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="93">
@@ -2609,16 +2609,16 @@
         <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F93" t="n">
         <v>0.0</v>
       </c>
       <c r="G93" t="n">
-        <v>36.0</v>
+        <v>14.0</v>
       </c>
       <c r="H93" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="94">
@@ -2626,13 +2626,13 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E94" t="s">
         <v>40</v>
@@ -2641,10 +2641,10 @@
         <v>0.0</v>
       </c>
       <c r="G94" t="n">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="H94" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="95">
@@ -2661,13 +2661,13 @@
         <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F95" t="n">
         <v>0.0</v>
       </c>
       <c r="G95" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2678,7 +2678,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2687,13 +2687,13 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G96" t="n">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2713,13 +2713,13 @@
         <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F97" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G97" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2739,7 +2739,7 @@
         <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F98" t="n">
         <v>0.0</v>
@@ -2765,13 +2765,13 @@
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F99" t="n">
         <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2782,7 +2782,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2791,13 +2791,13 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G100" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2817,10 +2817,10 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F101" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>
@@ -2834,7 +2834,7 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
         <v>16</v>
@@ -2843,13 +2843,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2869,13 +2869,13 @@
         <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F103" t="n">
         <v>0.0</v>
       </c>
       <c r="G103" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H103" t="n">
         <v>0.0</v>
@@ -2895,13 +2895,13 @@
         <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
       </c>
       <c r="G104" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H104" t="n">
         <v>0.0</v>
@@ -2912,25 +2912,25 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C105" t="s">
         <v>16</v>
       </c>
       <c r="D105" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G105" t="n">
         <v>4.0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="106">
@@ -2947,16 +2947,16 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F106" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G106" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H106" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -2973,13 +2973,13 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2990,7 +2990,7 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
@@ -2999,13 +2999,13 @@
         <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F108" t="n">
         <v>0.0</v>
       </c>
       <c r="G108" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3016,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -3025,7 +3025,7 @@
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F109" t="n">
         <v>0.0</v>
@@ -3051,7 +3051,7 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F110" t="n">
         <v>0.0</v>
@@ -3060,7 +3060,7 @@
         <v>1.0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="111">
@@ -3068,7 +3068,7 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C111" t="s">
         <v>16</v>
@@ -3077,16 +3077,16 @@
         <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="112">
@@ -3103,13 +3103,13 @@
         <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F112" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3129,13 +3129,13 @@
         <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F113" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G113" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3155,13 +3155,13 @@
         <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F114" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G114" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3172,22 +3172,22 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C115" t="s">
         <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F115" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G115" t="n">
-        <v>17.0</v>
+        <v>7.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3207,13 +3207,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F116" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G116" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3233,13 +3233,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F117" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G117" t="n">
-        <v>1.0</v>
+        <v>36.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3259,13 +3259,13 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F118" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G118" t="n">
-        <v>36.0</v>
+        <v>0.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3276,7 +3276,7 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C119" t="s">
         <v>16</v>
@@ -3285,10 +3285,10 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F119" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G119" t="n">
         <v>0.0</v>
@@ -3311,13 +3311,13 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F120" t="n">
         <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H120" t="n">
         <v>0.0</v>
@@ -3337,13 +3337,13 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F121" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G121" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3363,13 +3363,13 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F122" t="n">
         <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3380,7 +3380,7 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C123" t="s">
         <v>16</v>
@@ -3389,16 +3389,16 @@
         <v>33</v>
       </c>
       <c r="E123" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G123" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="124">
@@ -3415,16 +3415,16 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F124" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0</v>
+        <v>78.0</v>
       </c>
       <c r="H124" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="125">
@@ -3441,13 +3441,13 @@
         <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F125" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="G125" t="n">
-        <v>78.0</v>
+        <v>24.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3467,16 +3467,16 @@
         <v>33</v>
       </c>
       <c r="E126" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F126" t="n">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>24.0</v>
+        <v>476.0</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="127">
@@ -3493,16 +3493,16 @@
         <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F127" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G127" t="n">
-        <v>476.0</v>
+        <v>0.0</v>
       </c>
       <c r="H127" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="128">
@@ -3516,16 +3516,16 @@
         <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F128" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3545,13 +3545,13 @@
         <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F129" t="n">
         <v>1.0</v>
       </c>
       <c r="G129" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3571,13 +3571,13 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F130" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H130" t="n">
         <v>0.0</v>
@@ -3597,13 +3597,13 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n">
         <v>2.0</v>
       </c>
       <c r="G131" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>
@@ -3620,16 +3620,16 @@
         <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E132" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F132" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3649,16 +3649,16 @@
         <v>35</v>
       </c>
       <c r="E133" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F133" t="n">
         <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>7.0</v>
+        <v>16.0</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="134">
@@ -3675,16 +3675,16 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F134" t="n">
         <v>0.0</v>
       </c>
       <c r="G134" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="H134" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="135">
@@ -3692,22 +3692,22 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C135" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D135" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3727,13 +3727,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F136" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G136" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3753,13 +3753,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F137" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3779,13 +3779,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F138" t="n">
         <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3796,7 +3796,7 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
@@ -3805,13 +3805,13 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G139" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3831,13 +3831,13 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F140" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G140" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3857,13 +3857,13 @@
         <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F141" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G141" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G141" t="n">
-        <v>0.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3883,13 +3883,13 @@
         <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F142" t="n">
         <v>0.0</v>
       </c>
       <c r="G142" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3909,13 +3909,13 @@
         <v>36</v>
       </c>
       <c r="E143" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F143" t="n">
         <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3926,7 +3926,7 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3935,13 +3935,13 @@
         <v>36</v>
       </c>
       <c r="E144" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G144" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3952,7 +3952,7 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3961,10 +3961,10 @@
         <v>36</v>
       </c>
       <c r="E145" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F145" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -3987,13 +3987,13 @@
         <v>36</v>
       </c>
       <c r="E146" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F146" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4004,22 +4004,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G147" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4039,13 +4039,13 @@
         <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F148" t="n">
         <v>1.0</v>
       </c>
       <c r="G148" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4065,13 +4065,13 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F149" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4091,13 +4091,13 @@
         <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F150" t="n">
         <v>0.0</v>
       </c>
       <c r="G150" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4108,7 +4108,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4117,13 +4117,13 @@
         <v>37</v>
       </c>
       <c r="E151" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G151" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4143,13 +4143,13 @@
         <v>37</v>
       </c>
       <c r="E152" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F152" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4169,13 +4169,13 @@
         <v>37</v>
       </c>
       <c r="E153" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F153" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4195,7 +4195,7 @@
         <v>37</v>
       </c>
       <c r="E154" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F154" t="n">
         <v>0.0</v>
@@ -4212,22 +4212,22 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C155" t="s">
         <v>17</v>
       </c>
       <c r="D155" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G155" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4247,10 +4247,10 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F156" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G156" t="n">
         <v>0.0</v>
@@ -4273,13 +4273,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F157" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4299,13 +4299,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F158" t="n">
         <v>1.0</v>
       </c>
       <c r="G158" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4325,13 +4325,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F159" t="n">
         <v>1.0</v>
       </c>
       <c r="G159" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4342,7 +4342,7 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
@@ -4351,7 +4351,7 @@
         <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F160" t="n">
         <v>1.0</v>
@@ -4377,13 +4377,13 @@
         <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F161" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4394,22 +4394,22 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G162" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4429,13 +4429,13 @@
         <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F163" t="n">
         <v>1.0</v>
       </c>
       <c r="G163" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4455,13 +4455,13 @@
         <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F164" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G164" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4481,13 +4481,13 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F165" t="n">
         <v>0.0</v>
       </c>
       <c r="G165" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4498,7 +4498,7 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
@@ -4507,13 +4507,13 @@
         <v>39</v>
       </c>
       <c r="E166" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G166" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4533,10 +4533,10 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F167" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -4559,13 +4559,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F168" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4585,13 +4585,13 @@
         <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F169" t="n">
         <v>1.0</v>
       </c>
       <c r="G169" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4611,13 +4611,13 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F170" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G170" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4637,41 +4637,15 @@
         <v>39</v>
       </c>
       <c r="E171" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F171" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G171" t="n">
         <v>0.0</v>
       </c>
       <c r="H171" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>8</v>
-      </c>
-      <c r="B172" t="s">
-        <v>10</v>
-      </c>
-      <c r="C172" t="s">
-        <v>17</v>
-      </c>
-      <c r="D172" t="s">
-        <v>39</v>
-      </c>
-      <c r="E172" t="s">
-        <v>43</v>
-      </c>
-      <c r="F172" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H172" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Allevamenti_ZR.xlsx
+++ b/Download/Allevamenti_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="50">
   <si>
     <t>Area</t>
   </si>
@@ -122,10 +122,16 @@
     <t>VC</t>
   </si>
   <si>
+    <t>FI</t>
+  </si>
+  <si>
     <t>LU</t>
   </si>
   <si>
     <t>MS</t>
+  </si>
+  <si>
+    <t>PI</t>
   </si>
   <si>
     <t>PO</t>
@@ -243,7 +249,7 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
         <v>1.0</v>
@@ -269,7 +275,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -295,7 +301,7 @@
         <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
         <v>0.0</v>
@@ -321,7 +327,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -347,7 +353,7 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -373,7 +379,7 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
         <v>6.0</v>
@@ -399,7 +405,7 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
         <v>2.0</v>
@@ -425,7 +431,7 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
         <v>1.0</v>
@@ -451,7 +457,7 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -477,7 +483,7 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -503,7 +509,7 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -529,7 +535,7 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F13" t="n">
         <v>1.0</v>
@@ -555,13 +561,13 @@
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H14" t="n">
         <v>0.0</v>
@@ -581,13 +587,13 @@
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
       </c>
       <c r="G15" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="H15" t="n">
         <v>0.0</v>
@@ -607,7 +613,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -633,13 +639,13 @@
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H17" t="n">
         <v>0.0</v>
@@ -659,13 +665,13 @@
         <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F18" t="n">
         <v>0.0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H18" t="n">
         <v>0.0</v>
@@ -685,7 +691,7 @@
         <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -711,7 +717,7 @@
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -737,7 +743,7 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F21" t="n">
         <v>2.0</v>
@@ -763,7 +769,7 @@
         <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -789,7 +795,7 @@
         <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -815,7 +821,7 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -841,7 +847,7 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -867,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -893,7 +899,7 @@
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -919,7 +925,7 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -945,7 +951,7 @@
         <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -971,7 +977,7 @@
         <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -997,7 +1003,7 @@
         <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -1023,7 +1029,7 @@
         <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>
@@ -1049,7 +1055,7 @@
         <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>
@@ -1075,7 +1081,7 @@
         <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F34" t="n">
         <v>2.0</v>
@@ -1101,7 +1107,7 @@
         <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F35" t="n">
         <v>2.0</v>
@@ -1127,7 +1133,7 @@
         <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F36" t="n">
         <v>0.0</v>
@@ -1153,7 +1159,7 @@
         <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>
@@ -1179,7 +1185,7 @@
         <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F38" t="n">
         <v>0.0</v>
@@ -1205,7 +1211,7 @@
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>
@@ -1231,7 +1237,7 @@
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
@@ -1257,7 +1263,7 @@
         <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F41" t="n">
         <v>3.0</v>
@@ -1283,7 +1289,7 @@
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F42" t="n">
         <v>1.0</v>
@@ -1309,7 +1315,7 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F43" t="n">
         <v>0.0</v>
@@ -1335,7 +1341,7 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F44" t="n">
         <v>3.0</v>
@@ -1361,7 +1367,7 @@
         <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F45" t="n">
         <v>0.0</v>
@@ -1387,7 +1393,7 @@
         <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F46" t="n">
         <v>0.0</v>
@@ -1413,7 +1419,7 @@
         <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F47" t="n">
         <v>1.0</v>
@@ -1439,7 +1445,7 @@
         <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
@@ -1465,7 +1471,7 @@
         <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F49" t="n">
         <v>0.0</v>
@@ -1491,7 +1497,7 @@
         <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F50" t="n">
         <v>4.0</v>
@@ -1517,7 +1523,7 @@
         <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F51" t="n">
         <v>3.0</v>
@@ -1543,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F52" t="n">
         <v>1.0</v>
@@ -1569,7 +1575,7 @@
         <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F53" t="n">
         <v>0.0</v>
@@ -1595,7 +1601,7 @@
         <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F54" t="n">
         <v>1.0</v>
@@ -1621,7 +1627,7 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F55" t="n">
         <v>2.0</v>
@@ -1647,7 +1653,7 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>1.0</v>
@@ -1673,7 +1679,7 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F57" t="n">
         <v>3.0</v>
@@ -1699,7 +1705,7 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F58" t="n">
         <v>0.0</v>
@@ -1725,7 +1731,7 @@
         <v>25</v>
       </c>
       <c r="E59" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F59" t="n">
         <v>0.0</v>
@@ -1751,7 +1757,7 @@
         <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F60" t="n">
         <v>0.0</v>
@@ -1777,7 +1783,7 @@
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F61" t="n">
         <v>2.0</v>
@@ -1803,7 +1809,7 @@
         <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F62" t="n">
         <v>0.0</v>
@@ -1829,7 +1835,7 @@
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F63" t="n">
         <v>0.0</v>
@@ -1855,7 +1861,7 @@
         <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F64" t="n">
         <v>1.0</v>
@@ -1881,7 +1887,7 @@
         <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F65" t="n">
         <v>0.0</v>
@@ -1907,7 +1913,7 @@
         <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F66" t="n">
         <v>0.0</v>
@@ -1933,7 +1939,7 @@
         <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
@@ -1959,7 +1965,7 @@
         <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F68" t="n">
         <v>0.0</v>
@@ -1985,7 +1991,7 @@
         <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F69" t="n">
         <v>0.0</v>
@@ -2011,7 +2017,7 @@
         <v>27</v>
       </c>
       <c r="E70" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F70" t="n">
         <v>0.0</v>
@@ -2037,7 +2043,7 @@
         <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F71" t="n">
         <v>0.0</v>
@@ -2063,7 +2069,7 @@
         <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F72" t="n">
         <v>0.0</v>
@@ -2089,7 +2095,7 @@
         <v>28</v>
       </c>
       <c r="E73" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F73" t="n">
         <v>1.0</v>
@@ -2115,7 +2121,7 @@
         <v>28</v>
       </c>
       <c r="E74" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F74" t="n">
         <v>1.0</v>
@@ -2141,7 +2147,7 @@
         <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F75" t="n">
         <v>1.0</v>
@@ -2167,7 +2173,7 @@
         <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F76" t="n">
         <v>1.0</v>
@@ -2193,7 +2199,7 @@
         <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F77" t="n">
         <v>0.0</v>
@@ -2219,7 +2225,7 @@
         <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F78" t="n">
         <v>1.0</v>
@@ -2245,7 +2251,7 @@
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F79" t="n">
         <v>0.0</v>
@@ -2271,7 +2277,7 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
@@ -2297,7 +2303,7 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F81" t="n">
         <v>0.0</v>
@@ -2323,7 +2329,7 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F82" t="n">
         <v>1.0</v>
@@ -2349,7 +2355,7 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F83" t="n">
         <v>1.0</v>
@@ -2375,7 +2381,7 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F84" t="n">
         <v>0.0</v>
@@ -2401,7 +2407,7 @@
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F85" t="n">
         <v>0.0</v>
@@ -2427,7 +2433,7 @@
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F86" t="n">
         <v>1.0</v>
@@ -2453,7 +2459,7 @@
         <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F87" t="n">
         <v>0.0</v>
@@ -2479,7 +2485,7 @@
         <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F88" t="n">
         <v>0.0</v>
@@ -2505,7 +2511,7 @@
         <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F89" t="n">
         <v>1.0</v>
@@ -2531,7 +2537,7 @@
         <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F90" t="n">
         <v>2.0</v>
@@ -2557,7 +2563,7 @@
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F91" t="n">
         <v>0.0</v>
@@ -2583,7 +2589,7 @@
         <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F92" t="n">
         <v>0.0</v>
@@ -2609,7 +2615,7 @@
         <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F93" t="n">
         <v>0.0</v>
@@ -2635,7 +2641,7 @@
         <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F94" t="n">
         <v>0.0</v>
@@ -2661,7 +2667,7 @@
         <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F95" t="n">
         <v>0.0</v>
@@ -2687,7 +2693,7 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F96" t="n">
         <v>3.0</v>
@@ -2713,7 +2719,7 @@
         <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F97" t="n">
         <v>0.0</v>
@@ -2739,7 +2745,7 @@
         <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F98" t="n">
         <v>0.0</v>
@@ -2765,7 +2771,7 @@
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F99" t="n">
         <v>0.0</v>
@@ -2791,7 +2797,7 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F100" t="n">
         <v>1.0</v>
@@ -2817,7 +2823,7 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F101" t="n">
         <v>0.0</v>
@@ -2843,7 +2849,7 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
@@ -2869,7 +2875,7 @@
         <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F103" t="n">
         <v>0.0</v>
@@ -2895,7 +2901,7 @@
         <v>31</v>
       </c>
       <c r="E104" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
@@ -2921,7 +2927,7 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F105" t="n">
         <v>1.0</v>
@@ -2947,7 +2953,7 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F106" t="n">
         <v>0.0</v>
@@ -2973,7 +2979,7 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
@@ -2999,7 +3005,7 @@
         <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F108" t="n">
         <v>0.0</v>
@@ -3025,7 +3031,7 @@
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F109" t="n">
         <v>0.0</v>
@@ -3051,7 +3057,7 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F110" t="n">
         <v>0.0</v>
@@ -3077,7 +3083,7 @@
         <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F111" t="n">
         <v>1.0</v>
@@ -3103,7 +3109,7 @@
         <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F112" t="n">
         <v>3.0</v>
@@ -3129,7 +3135,7 @@
         <v>32</v>
       </c>
       <c r="E113" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F113" t="n">
         <v>6.0</v>
@@ -3155,7 +3161,7 @@
         <v>32</v>
       </c>
       <c r="E114" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F114" t="n">
         <v>2.0</v>
@@ -3181,7 +3187,7 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F115" t="n">
         <v>3.0</v>
@@ -3207,7 +3213,7 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F116" t="n">
         <v>4.0</v>
@@ -3233,7 +3239,7 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F117" t="n">
         <v>3.0</v>
@@ -3259,7 +3265,7 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F118" t="n">
         <v>2.0</v>
@@ -3285,7 +3291,7 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F119" t="n">
         <v>1.0</v>
@@ -3311,7 +3317,7 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F120" t="n">
         <v>1.0</v>
@@ -3337,7 +3343,7 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F121" t="n">
         <v>0.0</v>
@@ -3363,7 +3369,7 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F122" t="n">
         <v>0.0</v>
@@ -3389,7 +3395,7 @@
         <v>33</v>
       </c>
       <c r="E123" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F123" t="n">
         <v>1.0</v>
@@ -3415,7 +3421,7 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F124" t="n">
         <v>10.0</v>
@@ -3441,7 +3447,7 @@
         <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F125" t="n">
         <v>12.0</v>
@@ -3467,7 +3473,7 @@
         <v>33</v>
       </c>
       <c r="E126" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F126" t="n">
         <v>3.0</v>
@@ -3493,7 +3499,7 @@
         <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F127" t="n">
         <v>2.0</v>
@@ -3519,7 +3525,7 @@
         <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F128" t="n">
         <v>1.0</v>
@@ -3545,7 +3551,7 @@
         <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F129" t="n">
         <v>1.0</v>
@@ -3571,7 +3577,7 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F130" t="n">
         <v>2.0</v>
@@ -3597,7 +3603,7 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F131" t="n">
         <v>2.0</v>
@@ -3623,7 +3629,7 @@
         <v>35</v>
       </c>
       <c r="E132" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F132" t="n">
         <v>0.0</v>
@@ -3649,7 +3655,7 @@
         <v>35</v>
       </c>
       <c r="E133" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F133" t="n">
         <v>0.0</v>
@@ -3675,7 +3681,7 @@
         <v>35</v>
       </c>
       <c r="E134" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F134" t="n">
         <v>0.0</v>
@@ -3701,13 +3707,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F135" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G135" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3724,10 +3730,10 @@
         <v>17</v>
       </c>
       <c r="D136" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E136" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F136" t="n">
         <v>1.0</v>
@@ -3750,16 +3756,16 @@
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E137" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F137" t="n">
         <v>0.0</v>
       </c>
       <c r="G137" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3776,7 +3782,7 @@
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E138" t="s">
         <v>42</v>
@@ -3785,7 +3791,7 @@
         <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3796,19 +3802,19 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E139" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F139" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G139" t="n">
         <v>3.0</v>
@@ -3828,13 +3834,13 @@
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E140" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F140" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G140" t="n">
         <v>0.0</v>
@@ -3854,16 +3860,16 @@
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E141" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G141" t="n">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3880,16 +3886,16 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G142" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3906,10 +3912,10 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F143" t="n">
         <v>0.0</v>
@@ -3926,22 +3932,22 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F144" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3952,22 +3958,22 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F145" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3978,22 +3984,22 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E146" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G146" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4010,10 +4016,10 @@
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E147" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F147" t="n">
         <v>1.0</v>
@@ -4036,10 +4042,10 @@
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E148" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F148" t="n">
         <v>1.0</v>
@@ -4062,10 +4068,10 @@
         <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E149" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F149" t="n">
         <v>0.0</v>
@@ -4088,10 +4094,10 @@
         <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E150" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F150" t="n">
         <v>0.0</v>
@@ -4114,10 +4120,10 @@
         <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E151" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F151" t="n">
         <v>2.0</v>
@@ -4140,10 +4146,10 @@
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E152" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F152" t="n">
         <v>1.0</v>
@@ -4166,10 +4172,10 @@
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F153" t="n">
         <v>0.0</v>
@@ -4192,10 +4198,10 @@
         <v>17</v>
       </c>
       <c r="D154" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F154" t="n">
         <v>0.0</v>
@@ -4218,10 +4224,10 @@
         <v>17</v>
       </c>
       <c r="D155" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E155" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F155" t="n">
         <v>1.0</v>
@@ -4244,16 +4250,16 @@
         <v>17</v>
       </c>
       <c r="D156" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E156" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F156" t="n">
         <v>3.0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4270,10 +4276,10 @@
         <v>17</v>
       </c>
       <c r="D157" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E157" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F157" t="n">
         <v>1.0</v>
@@ -4296,13 +4302,13 @@
         <v>17</v>
       </c>
       <c r="D158" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E158" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F158" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G158" t="n">
         <v>1.0</v>
@@ -4322,16 +4328,16 @@
         <v>17</v>
       </c>
       <c r="D159" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E159" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F159" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4342,16 +4348,16 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E160" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F160" t="n">
         <v>1.0</v>
@@ -4368,22 +4374,22 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
       </c>
       <c r="D161" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E161" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G161" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4400,16 +4406,16 @@
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E162" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F162" t="n">
         <v>1.0</v>
       </c>
       <c r="G162" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4426,16 +4432,16 @@
         <v>17</v>
       </c>
       <c r="D163" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E163" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F163" t="n">
         <v>1.0</v>
       </c>
       <c r="G163" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4452,16 +4458,16 @@
         <v>17</v>
       </c>
       <c r="D164" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E164" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G164" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4472,22 +4478,22 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C165" t="s">
         <v>17</v>
       </c>
       <c r="D165" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E165" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G165" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4498,22 +4504,22 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
       </c>
       <c r="D166" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E166" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F166" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4524,22 +4530,22 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C167" t="s">
         <v>17</v>
       </c>
       <c r="D167" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E167" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F167" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G167" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G167" t="n">
-        <v>0.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>
@@ -4550,22 +4556,22 @@
         <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C168" t="s">
         <v>17</v>
       </c>
       <c r="D168" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E168" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F168" t="n">
         <v>1.0</v>
       </c>
       <c r="G168" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4576,22 +4582,22 @@
         <v>8</v>
       </c>
       <c r="B169" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C169" t="s">
         <v>17</v>
       </c>
       <c r="D169" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E169" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F169" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G169" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4602,22 +4608,22 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C170" t="s">
         <v>17</v>
       </c>
       <c r="D170" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E170" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F170" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4628,24 +4634,180 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
       </c>
       <c r="D171" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E171" t="s">
         <v>43</v>
       </c>
       <c r="F171" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H171" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" t="s">
+        <v>41</v>
+      </c>
+      <c r="E172" t="s">
+        <v>49</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>8</v>
+      </c>
+      <c r="B173" t="s">
+        <v>10</v>
+      </c>
+      <c r="C173" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" t="s">
+        <v>41</v>
+      </c>
+      <c r="E173" t="s">
+        <v>47</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>8</v>
+      </c>
+      <c r="B174" t="s">
+        <v>10</v>
+      </c>
+      <c r="C174" t="s">
+        <v>17</v>
+      </c>
+      <c r="D174" t="s">
+        <v>41</v>
+      </c>
+      <c r="E174" t="s">
+        <v>46</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175" t="s">
+        <v>10</v>
+      </c>
+      <c r="C175" t="s">
+        <v>17</v>
+      </c>
+      <c r="D175" t="s">
+        <v>41</v>
+      </c>
+      <c r="E175" t="s">
+        <v>43</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>8</v>
+      </c>
+      <c r="B176" t="s">
+        <v>10</v>
+      </c>
+      <c r="C176" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" t="s">
+        <v>41</v>
+      </c>
+      <c r="E176" t="s">
+        <v>44</v>
+      </c>
+      <c r="F176" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" t="s">
+        <v>10</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" t="s">
+        <v>41</v>
+      </c>
+      <c r="E177" t="s">
+        <v>45</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H177" t="n">
         <v>0.0</v>
       </c>
     </row>
